--- a/概要/ガントチャート_舞台劇.xlsx
+++ b/概要/ガントチャート_舞台劇.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2958A8A-2925-47D7-8D7C-4CC4FE14B090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A8E289-1155-4E69-BAC8-AEB8B977BCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="285" windowWidth="26265" windowHeight="14715" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="進捗確認表" sheetId="20" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="46">
   <si>
     <t>ガントチャート</t>
     <phoneticPr fontId="19"/>
@@ -356,6 +356,19 @@
       <t>アルファバン</t>
     </rPh>
     <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>ゲームループ</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>完了</t>
+  </si>
+  <si>
+    <t>作業中</t>
+  </si>
+  <si>
+    <t>保留</t>
   </si>
 </sst>
 </file>
@@ -979,7 +992,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
@@ -1092,9 +1105,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="20" fillId="36" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="54">
     <cellStyle name="20% - アクセント 1" xfId="31" builtinId="30" customBuiltin="1"/>
@@ -13424,7 +13434,7 @@
         <v>30</v>
       </c>
       <c r="B9" s="37">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="C9" s="34">
         <v>45900</v>
@@ -13436,7 +13446,9 @@
         <f>COUNT($G9:$DE9)</f>
         <v>7</v>
       </c>
-      <c r="F9" s="26"/>
+      <c r="F9" s="26" t="s">
+        <v>44</v>
+      </c>
       <c r="G9" s="1" t="str">
         <f>IF(AND(G$5&gt;=$C9,G$5&lt;=$D9),1,"")</f>
         <v/>
@@ -13489,31 +13501,31 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="T9" s="38">
+      <c r="T9" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="U9" s="38">
+      <c r="U9" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="V9" s="38">
+      <c r="V9" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="W9" s="38">
+      <c r="W9" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="X9" s="38">
+      <c r="X9" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="Y9" s="38">
+      <c r="Y9" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="Z9" s="38">
+      <c r="Z9" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -13867,7 +13879,9 @@
         <f>COUNT($G10:$DE10)</f>
         <v>7</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="26" t="s">
+        <v>44</v>
+      </c>
       <c r="G10" s="1" t="str">
         <f t="shared" ref="G10:V26" si="7">IF(AND(G$5&gt;=$C10,G$5&lt;=$D10),1,"")</f>
         <v/>
@@ -13920,31 +13934,31 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T10" s="38">
+      <c r="T10" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="U10" s="38">
+      <c r="U10" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="V10" s="38">
+      <c r="V10" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="W10" s="38">
+      <c r="W10" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="X10" s="38">
+      <c r="X10" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="Y10" s="38">
+      <c r="Y10" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="Z10" s="38">
+      <c r="Z10" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -14298,7 +14312,9 @@
         <f t="shared" ref="E11:E13" si="8">COUNT($G11:$DE11)</f>
         <v>7</v>
       </c>
-      <c r="F11" s="26"/>
+      <c r="F11" s="26" t="s">
+        <v>44</v>
+      </c>
       <c r="G11" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -14351,31 +14367,31 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T11" s="38">
+      <c r="T11" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="U11" s="38">
+      <c r="U11" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="V11" s="38">
+      <c r="V11" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="W11" s="38">
+      <c r="W11" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="X11" s="38">
+      <c r="X11" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="Y11" s="38">
+      <c r="Y11" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="Z11" s="38">
+      <c r="Z11" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -14727,7 +14743,9 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="F12" s="26"/>
+      <c r="F12" s="26" t="s">
+        <v>45</v>
+      </c>
       <c r="G12" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -14780,31 +14798,31 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="T12" s="38">
+      <c r="T12" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="U12" s="38">
+      <c r="U12" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="V12" s="38">
+      <c r="V12" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="W12" s="38">
+      <c r="W12" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="X12" s="38">
+      <c r="X12" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="Y12" s="38">
+      <c r="Y12" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="Z12" s="38">
+      <c r="Z12" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -21516,15 +21534,25 @@
       </c>
     </row>
     <row r="28" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="13"/>
-      <c r="B28" s="37"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
+      <c r="A28" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="37">
+        <v>1</v>
+      </c>
+      <c r="C28" s="34">
+        <v>45900</v>
+      </c>
+      <c r="D28" s="34">
+        <v>45906</v>
+      </c>
       <c r="E28" s="11">
         <f>COUNT($G28:$DE28)</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="26"/>
+        <v>7</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>43</v>
+      </c>
       <c r="G28" s="1" t="str">
         <f t="shared" si="21"/>
         <v/>
@@ -21577,33 +21605,33 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="T28" s="1" t="str">
+      <c r="T28" s="1">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="U28" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="U28" s="1">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="V28" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="V28" s="1">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="W28" s="1" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="X28" s="1" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="Y28" s="1" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="Z28" s="1" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="W28" s="1">
+        <f t="shared" si="20"/>
+        <v>1</v>
+      </c>
+      <c r="X28" s="1">
+        <f t="shared" si="20"/>
+        <v>1</v>
+      </c>
+      <c r="Y28" s="1">
+        <f t="shared" si="20"/>
+        <v>1</v>
+      </c>
+      <c r="Z28" s="1">
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="AA28" s="1" t="str">
         <f t="shared" si="20"/>

--- a/概要/ガントチャート_舞台劇.xlsx
+++ b/概要/ガントチャート_舞台劇.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
     <t>ガントチャート</t>
     <phoneticPr fontId="19"/>
@@ -273,6 +273,13 @@
   </si>
   <si>
     <t>保留</t>
+  </si>
+  <si>
+    <t>回避</t>
+    <rPh sb="0" eb="2">
+      <t>カイヒ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
   </si>
 </sst>
 </file>
@@ -2900,17 +2907,17 @@
         <v>20</v>
       </c>
       <c r="B9" s="37">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C9" s="34">
-        <v>45900</v>
+        <v>45916</v>
       </c>
       <c r="D9" s="34">
         <v>45924</v>
       </c>
       <c r="E9" s="11">
         <f>COUNT($G9:$DE9)</f>
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F9" s="26" t="s">
         <v>34</v>
@@ -2967,69 +2974,69 @@
         <f t="shared" si="79"/>
         <v/>
       </c>
-      <c r="T9" s="1">
+      <c r="T9" s="1" t="str">
         <f t="shared" si="79"/>
-        <v>1</v>
-      </c>
-      <c r="U9" s="1">
+        <v/>
+      </c>
+      <c r="U9" s="1" t="str">
         <f t="shared" si="79"/>
-        <v>1</v>
-      </c>
-      <c r="V9" s="1">
+        <v/>
+      </c>
+      <c r="V9" s="1" t="str">
         <f t="shared" si="79"/>
-        <v>1</v>
-      </c>
-      <c r="W9" s="1">
+        <v/>
+      </c>
+      <c r="W9" s="1" t="str">
         <f t="shared" si="77"/>
-        <v>1</v>
-      </c>
-      <c r="X9" s="1">
+        <v/>
+      </c>
+      <c r="X9" s="1" t="str">
         <f t="shared" si="77"/>
-        <v>1</v>
-      </c>
-      <c r="Y9" s="1">
+        <v/>
+      </c>
+      <c r="Y9" s="1" t="str">
         <f t="shared" si="77"/>
-        <v>1</v>
-      </c>
-      <c r="Z9" s="1">
+        <v/>
+      </c>
+      <c r="Z9" s="1" t="str">
         <f t="shared" si="77"/>
-        <v>1</v>
-      </c>
-      <c r="AA9" s="1">
+        <v/>
+      </c>
+      <c r="AA9" s="1" t="str">
         <f t="shared" si="77"/>
-        <v>1</v>
-      </c>
-      <c r="AB9" s="1">
+        <v/>
+      </c>
+      <c r="AB9" s="1" t="str">
         <f t="shared" si="77"/>
-        <v>1</v>
-      </c>
-      <c r="AC9" s="1">
+        <v/>
+      </c>
+      <c r="AC9" s="1" t="str">
         <f t="shared" si="77"/>
-        <v>1</v>
-      </c>
-      <c r="AD9" s="1">
+        <v/>
+      </c>
+      <c r="AD9" s="1" t="str">
         <f t="shared" si="77"/>
-        <v>1</v>
-      </c>
-      <c r="AE9" s="1">
+        <v/>
+      </c>
+      <c r="AE9" s="1" t="str">
         <f t="shared" si="77"/>
-        <v>1</v>
-      </c>
-      <c r="AF9" s="1">
+        <v/>
+      </c>
+      <c r="AF9" s="1" t="str">
         <f t="shared" si="77"/>
-        <v>1</v>
-      </c>
-      <c r="AG9" s="1">
+        <v/>
+      </c>
+      <c r="AG9" s="1" t="str">
         <f t="shared" si="77"/>
-        <v>1</v>
-      </c>
-      <c r="AH9" s="1">
+        <v/>
+      </c>
+      <c r="AH9" s="1" t="str">
         <f t="shared" si="77"/>
-        <v>1</v>
-      </c>
-      <c r="AI9" s="1">
+        <v/>
+      </c>
+      <c r="AI9" s="1" t="str">
         <f t="shared" si="77"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AJ9" s="1">
         <f t="shared" si="77"/>
@@ -3333,17 +3340,17 @@
         <v>21</v>
       </c>
       <c r="B10" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="34">
-        <v>45900</v>
+        <v>45916</v>
       </c>
       <c r="D10" s="34">
         <v>45924</v>
       </c>
       <c r="E10" s="11">
         <f>COUNT($G10:$DE10)</f>
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F10" s="26" t="s">
         <v>34</v>
@@ -3400,69 +3407,69 @@
         <f t="shared" si="80"/>
         <v/>
       </c>
-      <c r="T10" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="U10" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="V10" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="W10" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="X10" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="Y10" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="Z10" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AA10" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AB10" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AC10" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AD10" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AE10" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AF10" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AG10" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AH10" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AI10" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
+      <c r="T10" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="U10" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="V10" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="W10" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="X10" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="Y10" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="Z10" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AA10" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AB10" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AC10" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AD10" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AE10" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AF10" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AG10" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AH10" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AI10" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
       </c>
       <c r="AJ10" s="1">
         <f t="shared" si="80"/>
@@ -3769,17 +3776,17 @@
         <v>0</v>
       </c>
       <c r="C11" s="34">
-        <v>45900</v>
+        <v>45916</v>
       </c>
       <c r="D11" s="34">
         <v>45924</v>
       </c>
       <c r="E11" s="11">
         <f t="shared" ref="E11:E13" si="81">COUNT($G11:$DE11)</f>
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G11" s="1" t="str">
         <f t="shared" si="79"/>
@@ -3833,69 +3840,69 @@
         <f t="shared" si="80"/>
         <v/>
       </c>
-      <c r="T11" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="U11" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="V11" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="W11" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="X11" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="Y11" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="Z11" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AA11" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AB11" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AC11" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AD11" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AE11" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AF11" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AG11" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AH11" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AI11" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
+      <c r="T11" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="U11" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="V11" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="W11" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="X11" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="Y11" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="Z11" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AA11" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AB11" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AC11" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AD11" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AE11" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AF11" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AG11" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AH11" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AI11" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
       </c>
       <c r="AJ11" s="1">
         <f t="shared" si="80"/>
@@ -4198,16 +4205,18 @@
       <c r="A12" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="37"/>
+      <c r="B12" s="37">
+        <v>0</v>
+      </c>
       <c r="C12" s="34">
-        <v>45900</v>
+        <v>45916</v>
       </c>
       <c r="D12" s="34">
         <v>45924</v>
       </c>
       <c r="E12" s="11">
         <f t="shared" si="81"/>
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F12" s="26" t="s">
         <v>35</v>
@@ -4264,69 +4273,69 @@
         <f t="shared" si="80"/>
         <v/>
       </c>
-      <c r="T12" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="U12" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="V12" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="W12" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="X12" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="Y12" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="Z12" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AA12" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AB12" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AC12" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AD12" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AE12" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AF12" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AG12" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AH12" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AI12" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
+      <c r="T12" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="U12" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="V12" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="W12" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="X12" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="Y12" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="Z12" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AA12" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AB12" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AC12" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AD12" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AE12" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AF12" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AG12" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AH12" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AI12" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
       </c>
       <c r="AJ12" s="1">
         <f t="shared" si="80"/>
@@ -4626,15 +4635,25 @@
       </c>
     </row>
     <row r="13" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="12"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
+      <c r="A13" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="37">
+        <v>0.3</v>
+      </c>
+      <c r="C13" s="34">
+        <v>45916</v>
+      </c>
+      <c r="D13" s="34">
+        <v>45924</v>
+      </c>
       <c r="E13" s="11">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="26"/>
+        <v>9</v>
+      </c>
+      <c r="F13" s="26" t="s">
+        <v>34</v>
+      </c>
       <c r="G13" s="1" t="str">
         <f t="shared" si="79"/>
         <v/>
@@ -4751,41 +4770,41 @@
         <f t="shared" si="80"/>
         <v/>
       </c>
-      <c r="AJ13" s="1" t="str">
-        <f t="shared" si="80"/>
-        <v/>
-      </c>
-      <c r="AK13" s="1" t="str">
-        <f t="shared" si="80"/>
-        <v/>
-      </c>
-      <c r="AL13" s="1" t="str">
-        <f t="shared" si="80"/>
-        <v/>
-      </c>
-      <c r="AM13" s="1" t="str">
-        <f t="shared" si="80"/>
-        <v/>
-      </c>
-      <c r="AN13" s="1" t="str">
-        <f t="shared" si="80"/>
-        <v/>
-      </c>
-      <c r="AO13" s="1" t="str">
-        <f t="shared" si="80"/>
-        <v/>
-      </c>
-      <c r="AP13" s="1" t="str">
-        <f t="shared" si="80"/>
-        <v/>
-      </c>
-      <c r="AQ13" s="1" t="str">
-        <f t="shared" si="80"/>
-        <v/>
-      </c>
-      <c r="AR13" s="1" t="str">
-        <f t="shared" si="80"/>
-        <v/>
+      <c r="AJ13" s="1">
+        <f t="shared" si="80"/>
+        <v>1</v>
+      </c>
+      <c r="AK13" s="1">
+        <f t="shared" si="80"/>
+        <v>1</v>
+      </c>
+      <c r="AL13" s="1">
+        <f t="shared" si="80"/>
+        <v>1</v>
+      </c>
+      <c r="AM13" s="1">
+        <f t="shared" si="80"/>
+        <v>1</v>
+      </c>
+      <c r="AN13" s="1">
+        <f t="shared" si="80"/>
+        <v>1</v>
+      </c>
+      <c r="AO13" s="1">
+        <f t="shared" si="80"/>
+        <v>1</v>
+      </c>
+      <c r="AP13" s="1">
+        <f t="shared" si="80"/>
+        <v>1</v>
+      </c>
+      <c r="AQ13" s="1">
+        <f t="shared" si="80"/>
+        <v>1</v>
+      </c>
+      <c r="AR13" s="1">
+        <f t="shared" si="80"/>
+        <v>1</v>
       </c>
       <c r="AS13" s="1" t="str">
         <f t="shared" si="80"/>
@@ -12569,6 +12588,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847">
@@ -12584,15 +12612,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12615,6 +12634,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -12623,12 +12650,4 @@
     <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/概要/ガントチャート_舞台劇.xlsx
+++ b/概要/ガントチャート_舞台劇.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>ガントチャート</t>
     <phoneticPr fontId="19"/>
@@ -202,13 +202,6 @@
     <phoneticPr fontId="19"/>
   </si>
   <si>
-    <t>致命攻撃</t>
-    <rPh sb="0" eb="4">
-      <t>チメイコウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
     <t>敵AI</t>
     <rPh sb="0" eb="1">
       <t>テキ</t>
@@ -270,9 +263,6 @@
   </si>
   <si>
     <t>作業中</t>
-  </si>
-  <si>
-    <t>保留</t>
   </si>
   <si>
     <t>回避</t>
@@ -2920,7 +2910,7 @@
         <v>9</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G9" s="1" t="str">
         <f t="shared" ref="G9:V30" si="79">IF(AND(G$5&gt;=$C9,G$5&lt;=$D9),1,"")</f>
@@ -3353,7 +3343,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G10" s="1" t="str">
         <f t="shared" si="79"/>
@@ -3786,7 +3776,7 @@
         <v>9</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G11" s="1" t="str">
         <f t="shared" si="79"/>
@@ -4203,10 +4193,10 @@
     </row>
     <row r="12" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="12" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B12" s="37">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C12" s="34">
         <v>45916</v>
@@ -4219,7 +4209,7 @@
         <v>9</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G12" s="1" t="str">
         <f t="shared" si="79"/>
@@ -4635,25 +4625,11 @@
       </c>
     </row>
     <row r="13" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="37">
-        <v>0.3</v>
-      </c>
-      <c r="C13" s="34">
-        <v>45916</v>
-      </c>
-      <c r="D13" s="34">
-        <v>45924</v>
-      </c>
-      <c r="E13" s="11">
-        <f t="shared" si="81"/>
-        <v>9</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>34</v>
-      </c>
+      <c r="B13" s="37"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="26"/>
       <c r="G13" s="1" t="str">
         <f t="shared" si="79"/>
         <v/>
@@ -4770,41 +4746,41 @@
         <f t="shared" si="80"/>
         <v/>
       </c>
-      <c r="AJ13" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AK13" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AL13" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AM13" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AN13" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AO13" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AP13" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AQ13" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AR13" s="1">
-        <f t="shared" si="80"/>
-        <v>1</v>
+      <c r="AJ13" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AK13" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AL13" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AM13" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AN13" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AO13" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AP13" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AQ13" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="AR13" s="1" t="str">
+        <f t="shared" si="80"/>
+        <v/>
       </c>
       <c r="AS13" s="1" t="str">
         <f t="shared" si="80"/>
@@ -5069,7 +5045,7 @@
     </row>
     <row r="14" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -5491,7 +5467,7 @@
     </row>
     <row r="15" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" s="37"/>
       <c r="C15" s="34">
@@ -5920,7 +5896,7 @@
     </row>
     <row r="16" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B16" s="37"/>
       <c r="C16" s="34">
@@ -7616,7 +7592,7 @@
     </row>
     <row r="20" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="19"/>
@@ -8038,7 +8014,7 @@
     </row>
     <row r="21" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" s="37"/>
       <c r="C21" s="34"/>
@@ -8463,7 +8439,7 @@
     </row>
     <row r="22" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="37"/>
       <c r="C22" s="34"/>
@@ -10157,7 +10133,7 @@
     </row>
     <row r="26" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
@@ -10579,7 +10555,7 @@
     </row>
     <row r="27" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" s="37"/>
       <c r="C27" s="34">
@@ -11008,7 +10984,7 @@
     </row>
     <row r="28" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" s="37">
         <v>1</v>
@@ -11024,7 +11000,7 @@
         <v>7</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G28" s="1" t="str">
         <f t="shared" si="79"/>
@@ -12588,15 +12564,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847">
@@ -12612,6 +12579,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12634,14 +12610,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -12650,4 +12618,12 @@
     <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/概要/ガントチャート_舞台劇.xlsx
+++ b/概要/ガントチャート_舞台劇.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
   <si>
     <t>ガントチャート</t>
     <phoneticPr fontId="19"/>
@@ -3343,7 +3343,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G10" s="1" t="str">
         <f t="shared" si="79"/>
@@ -3772,11 +3772,11 @@
         <v>45924</v>
       </c>
       <c r="E11" s="11">
-        <f t="shared" ref="E11:E13" si="81">COUNT($G11:$DE11)</f>
+        <f t="shared" ref="E11:E12" si="81">COUNT($G11:$DE11)</f>
         <v>9</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G11" s="1" t="str">
         <f t="shared" si="79"/>
@@ -4209,7 +4209,7 @@
         <v>9</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G12" s="1" t="str">
         <f t="shared" si="79"/>
@@ -5480,7 +5480,9 @@
         <f>COUNT($G15:$DE15)</f>
         <v>4</v>
       </c>
-      <c r="F15" s="26"/>
+      <c r="F15" s="26" t="s">
+        <v>32</v>
+      </c>
       <c r="G15" s="1" t="str">
         <f t="shared" si="79"/>
         <v/>
@@ -5909,7 +5911,9 @@
         <f>COUNT($G16:$DE16)</f>
         <v>4</v>
       </c>
-      <c r="F16" s="26"/>
+      <c r="F16" s="26" t="s">
+        <v>32</v>
+      </c>
       <c r="G16" s="1" t="str">
         <f t="shared" si="79"/>
         <v/>
@@ -10562,13 +10566,15 @@
         <v>45930</v>
       </c>
       <c r="D27" s="34">
-        <v>45931</v>
+        <v>45945</v>
       </c>
       <c r="E27" s="11">
         <f>COUNT($G27:$DE27)</f>
-        <v>2</v>
-      </c>
-      <c r="F27" s="26"/>
+        <v>16</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>32</v>
+      </c>
       <c r="G27" s="1" t="str">
         <f t="shared" si="79"/>
         <v/>
@@ -10749,61 +10755,61 @@
         <f t="shared" si="91"/>
         <v>1</v>
       </c>
-      <c r="AZ27" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="BA27" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="BB27" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="BC27" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="BD27" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="BE27" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="BF27" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="BG27" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="BH27" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="BI27" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="BJ27" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="BK27" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="BL27" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="BM27" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
+      <c r="AZ27" s="1">
+        <f t="shared" si="91"/>
+        <v>1</v>
+      </c>
+      <c r="BA27" s="1">
+        <f t="shared" si="91"/>
+        <v>1</v>
+      </c>
+      <c r="BB27" s="1">
+        <f t="shared" si="91"/>
+        <v>1</v>
+      </c>
+      <c r="BC27" s="1">
+        <f t="shared" si="91"/>
+        <v>1</v>
+      </c>
+      <c r="BD27" s="1">
+        <f t="shared" si="91"/>
+        <v>1</v>
+      </c>
+      <c r="BE27" s="1">
+        <f t="shared" si="91"/>
+        <v>1</v>
+      </c>
+      <c r="BF27" s="1">
+        <f t="shared" si="91"/>
+        <v>1</v>
+      </c>
+      <c r="BG27" s="1">
+        <f t="shared" si="91"/>
+        <v>1</v>
+      </c>
+      <c r="BH27" s="1">
+        <f t="shared" si="91"/>
+        <v>1</v>
+      </c>
+      <c r="BI27" s="1">
+        <f t="shared" si="91"/>
+        <v>1</v>
+      </c>
+      <c r="BJ27" s="1">
+        <f t="shared" si="91"/>
+        <v>1</v>
+      </c>
+      <c r="BK27" s="1">
+        <f t="shared" si="91"/>
+        <v>1</v>
+      </c>
+      <c r="BL27" s="1">
+        <f t="shared" si="91"/>
+        <v>1</v>
+      </c>
+      <c r="BM27" s="1">
+        <f t="shared" si="91"/>
+        <v>1</v>
       </c>
       <c r="BN27" s="1" t="str">
         <f t="shared" si="91"/>
@@ -12564,6 +12570,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847">
@@ -12579,15 +12594,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12610,6 +12616,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -12618,12 +12632,4 @@
     <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/概要/ガントチャート_舞台劇.xlsx
+++ b/概要/ガントチャート_舞台劇.xlsx
@@ -561,7 +561,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -756,12 +756,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1092,12 +1086,12 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="20" fillId="36" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="20" fillId="34" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -14936,7 +14930,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="34">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="C37" s="31">
         <v>45947</v>
@@ -24562,15 +24556,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847">
@@ -24586,6 +24571,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24608,14 +24602,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -24624,4 +24610,12 @@
     <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/概要/ガントチャート_舞台劇.xlsx
+++ b/概要/ガントチャート_舞台劇.xlsx
@@ -10,7 +10,7 @@
     <sheet name="進捗確認表" sheetId="20" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">進捗確認表!$A$6:$F$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">進捗確認表!$A$6:$F$42</definedName>
     <definedName name="タスク_開始" localSheetId="0">#REF!</definedName>
     <definedName name="タスク_終了" localSheetId="0">#REF!</definedName>
     <definedName name="タスク_進捗状況" localSheetId="0">#REF!</definedName>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
   <si>
     <t>ガントチャート</t>
     <phoneticPr fontId="19"/>
@@ -202,9 +202,6 @@
     <t>完了</t>
   </si>
   <si>
-    <t>作業中</t>
-  </si>
-  <si>
     <t>回避</t>
     <rPh sb="0" eb="2">
       <t>カイヒ</t>
@@ -316,13 +313,6 @@
     <phoneticPr fontId="19"/>
   </si>
   <si>
-    <t>パリィ時のヒットストップ</t>
-    <rPh sb="3" eb="4">
-      <t>ジ</t>
-    </rPh>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
     <t>パリィ時のスロー</t>
     <rPh sb="3" eb="4">
       <t>ジ</t>
@@ -351,6 +341,23 @@
     <t>文字表示</t>
     <rPh sb="0" eb="4">
       <t>モジヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>攻撃パターン追加(</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>パリィ、攻撃のヒットストップ</t>
+    <rPh sb="4" eb="6">
+      <t>コウゲキ</t>
     </rPh>
     <phoneticPr fontId="19"/>
   </si>
@@ -760,7 +767,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -898,6 +905,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -970,7 +990,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
@@ -1072,9 +1092,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="20" fillId="35" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -1093,6 +1110,13 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="34" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -1622,7 +1646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:DE58"/>
+  <dimension ref="A1:DE60"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18.75" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="25.77734375" style="1" customWidth="1"/>
@@ -1641,7 +1665,7 @@
     </row>
     <row r="2" spans="1:109" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1651,7 +1675,7 @@
     </row>
     <row r="3" spans="1:109" x14ac:dyDescent="0.45">
       <c r="A3" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -2545,14 +2569,14 @@
       </c>
     </row>
     <row r="7" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="42"/>
+      <c r="A7" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="41"/>
       <c r="G7" s="1" t="str">
         <f t="shared" ref="G7" si="76">IF(AND(G$5&gt;=$C7,G$5&lt;=$D7),1,"")</f>
         <v/>
@@ -3001,7 +3025,7 @@
         <v>26</v>
       </c>
       <c r="G9" s="1" t="str">
-        <f t="shared" ref="G9:V28" si="79">IF(AND(G$5&gt;=$C9,G$5&lt;=$D9),1,"")</f>
+        <f t="shared" ref="G9:V29" si="79">IF(AND(G$5&gt;=$C9,G$5&lt;=$D9),1,"")</f>
         <v/>
       </c>
       <c r="H9" s="1" t="str">
@@ -4281,7 +4305,7 @@
     </row>
     <row r="12" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="34">
         <v>1</v>
@@ -4713,10 +4737,12 @@
       </c>
     </row>
     <row r="13" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="34"/>
+      <c r="A13" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="34">
+        <v>1</v>
+      </c>
       <c r="C13" s="31">
         <v>45954</v>
       </c>
@@ -4727,7 +4753,9 @@
         <f t="shared" si="81"/>
         <v>2</v>
       </c>
-      <c r="F13" s="24"/>
+      <c r="F13" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G13" s="1" t="str">
         <f t="shared" si="79"/>
         <v/>
@@ -5101,7 +5129,7 @@
         <v/>
       </c>
       <c r="CV13" s="1" t="str">
-        <f t="shared" ref="CV13:DE40" si="86">IF(AND(CV$5&gt;=$C13,CV$5&lt;=$D13),1,"")</f>
+        <f t="shared" ref="CV13:DE42" si="86">IF(AND(CV$5&gt;=$C13,CV$5&lt;=$D13),1,"")</f>
         <v/>
       </c>
       <c r="CW13" s="1" t="str">
@@ -5142,10 +5170,12 @@
       </c>
     </row>
     <row r="14" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="34"/>
+      <c r="A14" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="34">
+        <v>1</v>
+      </c>
       <c r="C14" s="31">
         <v>45954</v>
       </c>
@@ -5156,7 +5186,9 @@
         <f t="shared" si="81"/>
         <v>2</v>
       </c>
-      <c r="F14" s="24"/>
+      <c r="F14" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G14" s="1" t="str">
         <f t="shared" si="79"/>
         <v/>
@@ -5418,7 +5450,7 @@
         <v/>
       </c>
       <c r="BT14" s="1" t="str">
-        <f t="shared" ref="BT14:CI29" si="87">IF(AND(BT$5&gt;=$C14,BT$5&lt;=$D14),1,"")</f>
+        <f t="shared" ref="BT14:CI30" si="87">IF(AND(BT$5&gt;=$C14,BT$5&lt;=$D14),1,"")</f>
         <v/>
       </c>
       <c r="BU14" s="1" t="str">
@@ -5482,7 +5514,7 @@
         <v/>
       </c>
       <c r="CJ14" s="1" t="str">
-        <f t="shared" ref="CJ14:CY40" si="88">IF(AND(CJ$5&gt;=$C14,CJ$5&lt;=$D14),1,"")</f>
+        <f t="shared" ref="CJ14:CY42" si="88">IF(AND(CJ$5&gt;=$C14,CJ$5&lt;=$D14),1,"")</f>
         <v/>
       </c>
       <c r="CK14" s="1" t="str">
@@ -5572,9 +5604,11 @@
     </row>
     <row r="15" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="34"/>
+        <v>40</v>
+      </c>
+      <c r="B15" s="34">
+        <v>1</v>
+      </c>
       <c r="C15" s="31">
         <v>45956</v>
       </c>
@@ -5585,7 +5619,9 @@
         <f t="shared" si="81"/>
         <v>4</v>
       </c>
-      <c r="F15" s="24"/>
+      <c r="F15" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G15" s="1" t="str">
         <f t="shared" si="79"/>
         <v/>
@@ -6000,8 +6036,8 @@
       </c>
     </row>
     <row r="16" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="37" t="s">
-        <v>43</v>
+      <c r="A16" s="43" t="s">
+        <v>48</v>
       </c>
       <c r="B16" s="34"/>
       <c r="C16" s="31">
@@ -6429,8 +6465,8 @@
       </c>
     </row>
     <row r="17" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="37" t="s">
-        <v>44</v>
+      <c r="A17" s="43" t="s">
+        <v>42</v>
       </c>
       <c r="B17" s="34"/>
       <c r="C17" s="31">
@@ -6697,7 +6733,7 @@
         <v/>
       </c>
       <c r="BR17" s="1" t="str">
-        <f t="shared" ref="BR17:CG43" si="89">IF(AND(BR$5&gt;=$C17,BR$5&lt;=$D17),1,"")</f>
+        <f t="shared" ref="BR17:CG45" si="89">IF(AND(BR$5&gt;=$C17,BR$5&lt;=$D17),1,"")</f>
         <v/>
       </c>
       <c r="BS17" s="1" t="str">
@@ -6858,434 +6894,20 @@
       </c>
     </row>
     <row r="18" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="37"/>
+      <c r="A18" s="43"/>
       <c r="B18" s="34"/>
       <c r="C18" s="31"/>
       <c r="D18" s="31"/>
       <c r="E18" s="9"/>
       <c r="F18" s="24"/>
-      <c r="G18" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="H18" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="I18" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="J18" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="K18" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="L18" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="M18" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="N18" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="O18" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="P18" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="Q18" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="R18" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="S18" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="T18" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="U18" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="V18" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="W18" s="1" t="str">
-        <f t="shared" ref="W18:AL44" si="90">IF(AND(W$5&gt;=$C18,W$5&lt;=$D18),1,"")</f>
-        <v/>
-      </c>
-      <c r="X18" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="Y18" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="Z18" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AA18" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AB18" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AC18" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AD18" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AE18" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AF18" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AG18" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AH18" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AI18" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AJ18" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AK18" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AL18" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AM18" s="1" t="str">
-        <f t="shared" ref="AM18:BB33" si="91">IF(AND(AM$5&gt;=$C18,AM$5&lt;=$D18),1,"")</f>
-        <v/>
-      </c>
-      <c r="AN18" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AO18" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AP18" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AQ18" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AR18" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AS18" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AT18" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AU18" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AV18" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AW18" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AX18" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AY18" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AZ18" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="BA18" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="BB18" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="BC18" s="1" t="str">
-        <f t="shared" ref="BC18:BR44" si="92">IF(AND(BC$5&gt;=$C18,BC$5&lt;=$D18),1,"")</f>
-        <v/>
-      </c>
-      <c r="BD18" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BE18" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BF18" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BG18" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BH18" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BI18" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BJ18" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BK18" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BL18" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BM18" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BN18" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BO18" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BP18" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BQ18" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BR18" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BS18" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BT18" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BU18" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BV18" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BW18" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BX18" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BY18" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BZ18" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="CA18" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="CB18" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="CC18" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="CD18" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="CE18" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="CF18" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="CG18" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="CH18" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="CI18" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="CJ18" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CK18" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CL18" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CM18" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CN18" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CO18" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CP18" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CQ18" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CR18" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CS18" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CT18" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CU18" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CV18" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CW18" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CX18" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CY18" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CZ18" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-      <c r="DA18" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-      <c r="DB18" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-      <c r="DC18" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-      <c r="DD18" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-      <c r="DE18" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
     </row>
     <row r="19" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="25"/>
+      <c r="A19" s="36"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="24"/>
       <c r="G19" s="1" t="str">
         <f t="shared" si="79"/>
         <v/>
@@ -7351,7 +6973,7 @@
         <v/>
       </c>
       <c r="W19" s="1" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" ref="W19:AL46" si="90">IF(AND(W$5&gt;=$C19,W$5&lt;=$D19),1,"")</f>
         <v/>
       </c>
       <c r="X19" s="1" t="str">
@@ -7415,7 +7037,7 @@
         <v/>
       </c>
       <c r="AM19" s="1" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" ref="AM19:BB34" si="91">IF(AND(AM$5&gt;=$C19,AM$5&lt;=$D19),1,"")</f>
         <v/>
       </c>
       <c r="AN19" s="1" t="str">
@@ -7479,7 +7101,7 @@
         <v/>
       </c>
       <c r="BC19" s="1" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" ref="BC19:BR46" si="92">IF(AND(BC$5&gt;=$C19,BC$5&lt;=$D19),1,"")</f>
         <v/>
       </c>
       <c r="BD19" s="1" t="str">
@@ -7700,23 +7322,14 @@
       </c>
     </row>
     <row r="20" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="34"/>
-      <c r="C20" s="31">
-        <v>45925</v>
-      </c>
-      <c r="D20" s="31">
-        <v>45928</v>
-      </c>
-      <c r="E20" s="9">
-        <f>COUNT($G20:$DE20)</f>
-        <v>4</v>
-      </c>
-      <c r="F20" s="24" t="s">
-        <v>26</v>
-      </c>
+      <c r="A20" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="25"/>
       <c r="G20" s="1" t="str">
         <f t="shared" si="79"/>
         <v/>
@@ -7869,21 +7482,21 @@
         <f t="shared" si="91"/>
         <v/>
       </c>
-      <c r="AS20" s="1">
-        <f t="shared" si="91"/>
-        <v>1</v>
-      </c>
-      <c r="AT20" s="1">
-        <f t="shared" si="91"/>
-        <v>1</v>
-      </c>
-      <c r="AU20" s="1">
-        <f t="shared" si="91"/>
-        <v>1</v>
-      </c>
-      <c r="AV20" s="1">
-        <f t="shared" si="91"/>
-        <v>1</v>
+      <c r="AS20" s="1" t="str">
+        <f t="shared" si="91"/>
+        <v/>
+      </c>
+      <c r="AT20" s="1" t="str">
+        <f t="shared" si="91"/>
+        <v/>
+      </c>
+      <c r="AU20" s="1" t="str">
+        <f t="shared" si="91"/>
+        <v/>
+      </c>
+      <c r="AV20" s="1" t="str">
+        <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="AW20" s="1" t="str">
         <f t="shared" si="91"/>
@@ -8132,9 +7745,11 @@
     </row>
     <row r="21" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="34"/>
+        <v>19</v>
+      </c>
+      <c r="B21" s="34">
+        <v>1</v>
+      </c>
       <c r="C21" s="31">
         <v>45925</v>
       </c>
@@ -8142,7 +7757,7 @@
         <v>45928</v>
       </c>
       <c r="E21" s="9">
-        <f t="shared" ref="E21:E26" si="93">COUNT($G21:$DE21)</f>
+        <f>COUNT($G21:$DE21)</f>
         <v>4</v>
       </c>
       <c r="F21" s="24" t="s">
@@ -8563,443 +8178,457 @@
     </row>
     <row r="22" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="34"/>
+        <v>23</v>
+      </c>
+      <c r="B22" s="34">
+        <v>1</v>
+      </c>
       <c r="C22" s="31">
+        <v>45925</v>
+      </c>
+      <c r="D22" s="31">
+        <v>45928</v>
+      </c>
+      <c r="E22" s="9">
+        <f t="shared" ref="E22:E27" si="93">COUNT($G22:$DE22)</f>
+        <v>4</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="1" t="str">
+        <f t="shared" si="79"/>
+        <v/>
+      </c>
+      <c r="H22" s="1" t="str">
+        <f t="shared" si="79"/>
+        <v/>
+      </c>
+      <c r="I22" s="1" t="str">
+        <f t="shared" si="79"/>
+        <v/>
+      </c>
+      <c r="J22" s="1" t="str">
+        <f t="shared" si="79"/>
+        <v/>
+      </c>
+      <c r="K22" s="1" t="str">
+        <f t="shared" si="79"/>
+        <v/>
+      </c>
+      <c r="L22" s="1" t="str">
+        <f t="shared" si="79"/>
+        <v/>
+      </c>
+      <c r="M22" s="1" t="str">
+        <f t="shared" si="79"/>
+        <v/>
+      </c>
+      <c r="N22" s="1" t="str">
+        <f t="shared" si="79"/>
+        <v/>
+      </c>
+      <c r="O22" s="1" t="str">
+        <f t="shared" si="79"/>
+        <v/>
+      </c>
+      <c r="P22" s="1" t="str">
+        <f t="shared" si="79"/>
+        <v/>
+      </c>
+      <c r="Q22" s="1" t="str">
+        <f t="shared" si="79"/>
+        <v/>
+      </c>
+      <c r="R22" s="1" t="str">
+        <f t="shared" si="79"/>
+        <v/>
+      </c>
+      <c r="S22" s="1" t="str">
+        <f t="shared" si="79"/>
+        <v/>
+      </c>
+      <c r="T22" s="1" t="str">
+        <f t="shared" si="79"/>
+        <v/>
+      </c>
+      <c r="U22" s="1" t="str">
+        <f t="shared" si="79"/>
+        <v/>
+      </c>
+      <c r="V22" s="1" t="str">
+        <f t="shared" si="79"/>
+        <v/>
+      </c>
+      <c r="W22" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="X22" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="Y22" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="Z22" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="AA22" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="AB22" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="AC22" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="AD22" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="AE22" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="AF22" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="AG22" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="AH22" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="AI22" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="AJ22" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="AK22" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="AL22" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="AM22" s="1" t="str">
+        <f t="shared" si="91"/>
+        <v/>
+      </c>
+      <c r="AN22" s="1" t="str">
+        <f t="shared" si="91"/>
+        <v/>
+      </c>
+      <c r="AO22" s="1" t="str">
+        <f t="shared" si="91"/>
+        <v/>
+      </c>
+      <c r="AP22" s="1" t="str">
+        <f t="shared" si="91"/>
+        <v/>
+      </c>
+      <c r="AQ22" s="1" t="str">
+        <f t="shared" si="91"/>
+        <v/>
+      </c>
+      <c r="AR22" s="1" t="str">
+        <f t="shared" si="91"/>
+        <v/>
+      </c>
+      <c r="AS22" s="1">
+        <f t="shared" si="91"/>
+        <v>1</v>
+      </c>
+      <c r="AT22" s="1">
+        <f t="shared" si="91"/>
+        <v>1</v>
+      </c>
+      <c r="AU22" s="1">
+        <f t="shared" si="91"/>
+        <v>1</v>
+      </c>
+      <c r="AV22" s="1">
+        <f t="shared" si="91"/>
+        <v>1</v>
+      </c>
+      <c r="AW22" s="1" t="str">
+        <f t="shared" si="91"/>
+        <v/>
+      </c>
+      <c r="AX22" s="1" t="str">
+        <f t="shared" si="91"/>
+        <v/>
+      </c>
+      <c r="AY22" s="1" t="str">
+        <f t="shared" si="91"/>
+        <v/>
+      </c>
+      <c r="AZ22" s="1" t="str">
+        <f t="shared" si="91"/>
+        <v/>
+      </c>
+      <c r="BA22" s="1" t="str">
+        <f t="shared" si="91"/>
+        <v/>
+      </c>
+      <c r="BB22" s="1" t="str">
+        <f t="shared" si="91"/>
+        <v/>
+      </c>
+      <c r="BC22" s="1" t="str">
+        <f t="shared" si="92"/>
+        <v/>
+      </c>
+      <c r="BD22" s="1" t="str">
+        <f t="shared" si="92"/>
+        <v/>
+      </c>
+      <c r="BE22" s="1" t="str">
+        <f t="shared" si="92"/>
+        <v/>
+      </c>
+      <c r="BF22" s="1" t="str">
+        <f t="shared" si="92"/>
+        <v/>
+      </c>
+      <c r="BG22" s="1" t="str">
+        <f t="shared" si="92"/>
+        <v/>
+      </c>
+      <c r="BH22" s="1" t="str">
+        <f t="shared" si="92"/>
+        <v/>
+      </c>
+      <c r="BI22" s="1" t="str">
+        <f t="shared" si="92"/>
+        <v/>
+      </c>
+      <c r="BJ22" s="1" t="str">
+        <f t="shared" si="92"/>
+        <v/>
+      </c>
+      <c r="BK22" s="1" t="str">
+        <f t="shared" si="92"/>
+        <v/>
+      </c>
+      <c r="BL22" s="1" t="str">
+        <f t="shared" si="92"/>
+        <v/>
+      </c>
+      <c r="BM22" s="1" t="str">
+        <f t="shared" si="92"/>
+        <v/>
+      </c>
+      <c r="BN22" s="1" t="str">
+        <f t="shared" si="92"/>
+        <v/>
+      </c>
+      <c r="BO22" s="1" t="str">
+        <f t="shared" si="92"/>
+        <v/>
+      </c>
+      <c r="BP22" s="1" t="str">
+        <f t="shared" si="92"/>
+        <v/>
+      </c>
+      <c r="BQ22" s="1" t="str">
+        <f t="shared" si="92"/>
+        <v/>
+      </c>
+      <c r="BR22" s="1" t="str">
+        <f t="shared" si="92"/>
+        <v/>
+      </c>
+      <c r="BS22" s="1" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="BT22" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BU22" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BV22" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BW22" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BX22" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BY22" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BZ22" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="CA22" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="CB22" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="CC22" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="CD22" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="CE22" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="CF22" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="CG22" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="CH22" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="CI22" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="CJ22" s="1" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="CK22" s="1" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="CL22" s="1" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="CM22" s="1" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="CN22" s="1" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="CO22" s="1" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="CP22" s="1" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="CQ22" s="1" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="CR22" s="1" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="CS22" s="1" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="CT22" s="1" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="CU22" s="1" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="CV22" s="1" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="CW22" s="1" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="CX22" s="1" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="CY22" s="1" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="CZ22" s="1" t="str">
+        <f t="shared" si="86"/>
+        <v/>
+      </c>
+      <c r="DA22" s="1" t="str">
+        <f t="shared" si="86"/>
+        <v/>
+      </c>
+      <c r="DB22" s="1" t="str">
+        <f t="shared" si="86"/>
+        <v/>
+      </c>
+      <c r="DC22" s="1" t="str">
+        <f t="shared" si="86"/>
+        <v/>
+      </c>
+      <c r="DD22" s="1" t="str">
+        <f t="shared" si="86"/>
+        <v/>
+      </c>
+      <c r="DE22" s="1" t="str">
+        <f t="shared" si="86"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="34">
+        <v>1</v>
+      </c>
+      <c r="C23" s="31">
         <v>45956</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D23" s="31">
         <v>45959</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E23" s="9">
         <f t="shared" si="93"/>
         <v>4</v>
       </c>
-      <c r="F22" s="24"/>
-      <c r="G22" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="H22" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="I22" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="J22" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="K22" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="L22" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="M22" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="N22" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="O22" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="P22" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="Q22" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="R22" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="S22" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="T22" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="U22" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="V22" s="1" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="W22" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="X22" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="Y22" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="Z22" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AA22" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AB22" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AC22" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AD22" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AE22" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AF22" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AG22" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AH22" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AI22" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AJ22" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AK22" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AL22" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AM22" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AN22" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AO22" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AP22" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AQ22" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AR22" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AS22" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AT22" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AU22" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AV22" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AW22" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AX22" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AY22" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="AZ22" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="BA22" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="BB22" s="1" t="str">
-        <f t="shared" si="91"/>
-        <v/>
-      </c>
-      <c r="BC22" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BD22" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BE22" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BF22" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BG22" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BH22" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BI22" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BJ22" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BK22" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BL22" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BM22" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BN22" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BO22" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BP22" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BQ22" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BR22" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BS22" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BT22" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BU22" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BV22" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BW22" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BX22" s="1">
-        <f t="shared" si="87"/>
-        <v>1</v>
-      </c>
-      <c r="BY22" s="1">
-        <f t="shared" si="87"/>
-        <v>1</v>
-      </c>
-      <c r="BZ22" s="1">
-        <f t="shared" si="87"/>
-        <v>1</v>
-      </c>
-      <c r="CA22" s="1">
-        <f t="shared" si="87"/>
-        <v>1</v>
-      </c>
-      <c r="CB22" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="CC22" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="CD22" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="CE22" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="CF22" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="CG22" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="CH22" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="CI22" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="CJ22" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CK22" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CL22" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CM22" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CN22" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CO22" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CP22" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CQ22" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CR22" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CS22" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CT22" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CU22" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CV22" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CW22" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CX22" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CY22" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CZ22" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-      <c r="DA22" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-      <c r="DB22" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-      <c r="DC22" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-      <c r="DD22" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-      <c r="DE22" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="11"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="9">
-        <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="F23" s="24"/>
+      <c r="F23" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G23" s="1" t="str">
         <f t="shared" si="79"/>
         <v/>
@@ -9276,21 +8905,21 @@
         <f t="shared" si="87"/>
         <v/>
       </c>
-      <c r="BX23" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BY23" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BZ23" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="CA23" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
+      <c r="BX23" s="1">
+        <f t="shared" si="87"/>
+        <v>1</v>
+      </c>
+      <c r="BY23" s="1">
+        <f t="shared" si="87"/>
+        <v>1</v>
+      </c>
+      <c r="BZ23" s="1">
+        <f t="shared" si="87"/>
+        <v>1</v>
+      </c>
+      <c r="CA23" s="1">
+        <f t="shared" si="87"/>
+        <v>1</v>
       </c>
       <c r="CB23" s="1" t="str">
         <f t="shared" si="87"/>
@@ -9414,7 +9043,9 @@
       </c>
     </row>
     <row r="24" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="11"/>
+      <c r="A24" s="11" t="s">
+        <v>47</v>
+      </c>
       <c r="B24" s="34"/>
       <c r="C24" s="31"/>
       <c r="D24" s="31"/>
@@ -10683,14 +10314,15 @@
       </c>
     </row>
     <row r="27" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="25"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="9">
+        <f t="shared" si="93"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="24"/>
       <c r="G27" s="1" t="str">
         <f t="shared" si="79"/>
         <v/>
@@ -11105,17 +10737,14 @@
       </c>
     </row>
     <row r="28" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="9">
-        <f>COUNT($G28:$DE28)</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="24"/>
+      <c r="A28" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="25"/>
       <c r="G28" s="1" t="str">
         <f t="shared" si="79"/>
         <v/>
@@ -11161,67 +10790,67 @@
         <v/>
       </c>
       <c r="R28" s="1" t="str">
-        <f t="shared" ref="R28:AG40" si="94">IF(AND(R$5&gt;=$C28,R$5&lt;=$D28),1,"")</f>
+        <f t="shared" si="79"/>
         <v/>
       </c>
       <c r="S28" s="1" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="79"/>
         <v/>
       </c>
       <c r="T28" s="1" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="79"/>
         <v/>
       </c>
       <c r="U28" s="1" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="79"/>
         <v/>
       </c>
       <c r="V28" s="1" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="79"/>
         <v/>
       </c>
       <c r="W28" s="1" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="X28" s="1" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="Y28" s="1" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="Z28" s="1" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="AA28" s="1" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="AB28" s="1" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="AC28" s="1" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="AD28" s="1" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="AE28" s="1" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="AF28" s="1" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="AG28" s="1" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="AH28" s="1" t="str">
@@ -11531,7 +11160,7 @@
     </row>
     <row r="29" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B29" s="34"/>
       <c r="C29" s="31"/>
@@ -11542,67 +11171,67 @@
       </c>
       <c r="F29" s="24"/>
       <c r="G29" s="1" t="str">
-        <f t="shared" ref="G29:V41" si="95">IF(AND(G$5&gt;=$C29,G$5&lt;=$D29),1,"")</f>
+        <f t="shared" si="79"/>
         <v/>
       </c>
       <c r="H29" s="1" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="79"/>
         <v/>
       </c>
       <c r="I29" s="1" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="79"/>
         <v/>
       </c>
       <c r="J29" s="1" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="79"/>
         <v/>
       </c>
       <c r="K29" s="1" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="79"/>
         <v/>
       </c>
       <c r="L29" s="1" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="79"/>
         <v/>
       </c>
       <c r="M29" s="1" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="79"/>
         <v/>
       </c>
       <c r="N29" s="1" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="79"/>
         <v/>
       </c>
       <c r="O29" s="1" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="79"/>
         <v/>
       </c>
       <c r="P29" s="1" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="79"/>
         <v/>
       </c>
       <c r="Q29" s="1" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="79"/>
         <v/>
       </c>
       <c r="R29" s="1" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" ref="R29:AG42" si="94">IF(AND(R$5&gt;=$C29,R$5&lt;=$D29),1,"")</f>
         <v/>
       </c>
       <c r="S29" s="1" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="T29" s="1" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="U29" s="1" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="V29" s="1" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="W29" s="1" t="str">
@@ -11862,67 +11491,67 @@
         <v/>
       </c>
       <c r="CI29" s="1" t="str">
-        <f t="shared" ref="CI29:CX41" si="96">IF(AND(CI$5&gt;=$C29,CI$5&lt;=$D29),1,"")</f>
+        <f t="shared" si="87"/>
         <v/>
       </c>
       <c r="CJ29" s="1" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="CK29" s="1" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="CL29" s="1" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="CM29" s="1" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="CN29" s="1" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="CO29" s="1" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="CP29" s="1" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="CQ29" s="1" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="CR29" s="1" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="CS29" s="1" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="CT29" s="1" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="CU29" s="1" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="CV29" s="1" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="CW29" s="1" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="CX29" s="1" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="CY29" s="1" t="str">
@@ -11955,17 +11584,19 @@
       </c>
     </row>
     <row r="30" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="11"/>
+      <c r="A30" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="B30" s="34"/>
       <c r="C30" s="31"/>
       <c r="D30" s="31"/>
       <c r="E30" s="9">
-        <f t="shared" ref="E30:E32" si="97">COUNT($G30:$DE30)</f>
+        <f>COUNT($G30:$DE30)</f>
         <v>0</v>
       </c>
       <c r="F30" s="24"/>
       <c r="G30" s="1" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" ref="G30:V43" si="95">IF(AND(G$5&gt;=$C30,G$5&lt;=$D30),1,"")</f>
         <v/>
       </c>
       <c r="H30" s="1" t="str">
@@ -12225,123 +11856,123 @@
         <v/>
       </c>
       <c r="BT30" s="1" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v/>
       </c>
       <c r="BU30" s="1" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v/>
       </c>
       <c r="BV30" s="1" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v/>
       </c>
       <c r="BW30" s="1" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v/>
       </c>
       <c r="BX30" s="1" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v/>
       </c>
       <c r="BY30" s="1" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v/>
       </c>
       <c r="BZ30" s="1" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v/>
       </c>
       <c r="CA30" s="1" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v/>
       </c>
       <c r="CB30" s="1" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v/>
       </c>
       <c r="CC30" s="1" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v/>
       </c>
       <c r="CD30" s="1" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v/>
       </c>
       <c r="CE30" s="1" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v/>
       </c>
       <c r="CF30" s="1" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v/>
       </c>
       <c r="CG30" s="1" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v/>
       </c>
       <c r="CH30" s="1" t="str">
-        <f t="shared" ref="CH30:CW42" si="98">IF(AND(CH$5&gt;=$C30,CH$5&lt;=$D30),1,"")</f>
+        <f t="shared" si="87"/>
         <v/>
       </c>
       <c r="CI30" s="1" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" ref="CI30:CX43" si="96">IF(AND(CI$5&gt;=$C30,CI$5&lt;=$D30),1,"")</f>
         <v/>
       </c>
       <c r="CJ30" s="1" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v/>
       </c>
       <c r="CK30" s="1" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v/>
       </c>
       <c r="CL30" s="1" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v/>
       </c>
       <c r="CM30" s="1" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v/>
       </c>
       <c r="CN30" s="1" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v/>
       </c>
       <c r="CO30" s="1" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v/>
       </c>
       <c r="CP30" s="1" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v/>
       </c>
       <c r="CQ30" s="1" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v/>
       </c>
       <c r="CR30" s="1" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v/>
       </c>
       <c r="CS30" s="1" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v/>
       </c>
       <c r="CT30" s="1" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v/>
       </c>
       <c r="CU30" s="1" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v/>
       </c>
       <c r="CV30" s="1" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v/>
       </c>
       <c r="CW30" s="1" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v/>
       </c>
       <c r="CX30" s="1" t="str">
@@ -12383,7 +12014,7 @@
       <c r="C31" s="31"/>
       <c r="D31" s="31"/>
       <c r="E31" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" ref="E31:E33" si="97">COUNT($G31:$DE31)</f>
         <v>0</v>
       </c>
       <c r="F31" s="24"/>
@@ -12704,7 +12335,7 @@
         <v/>
       </c>
       <c r="CH31" s="1" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" ref="CH31:CW44" si="98">IF(AND(CH$5&gt;=$C31,CH$5&lt;=$D31),1,"")</f>
         <v/>
       </c>
       <c r="CI31" s="1" t="str">
@@ -13224,14 +12855,15 @@
       </c>
     </row>
     <row r="33" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="25"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="9">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="24"/>
       <c r="G33" s="1" t="str">
         <f t="shared" si="95"/>
         <v/>
@@ -13421,67 +13053,67 @@
         <v/>
       </c>
       <c r="BB33" s="1" t="str">
-        <f t="shared" ref="BB33:BQ44" si="99">IF(AND(BB$5&gt;=$C33,BB$5&lt;=$D33),1,"")</f>
+        <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="BC33" s="1" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v/>
       </c>
       <c r="BD33" s="1" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v/>
       </c>
       <c r="BE33" s="1" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v/>
       </c>
       <c r="BF33" s="1" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v/>
       </c>
       <c r="BG33" s="1" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v/>
       </c>
       <c r="BH33" s="1" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v/>
       </c>
       <c r="BI33" s="1" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v/>
       </c>
       <c r="BJ33" s="1" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v/>
       </c>
       <c r="BK33" s="1" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v/>
       </c>
       <c r="BL33" s="1" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v/>
       </c>
       <c r="BM33" s="1" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v/>
       </c>
       <c r="BN33" s="1" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v/>
       </c>
       <c r="BO33" s="1" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v/>
       </c>
       <c r="BP33" s="1" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v/>
       </c>
       <c r="BQ33" s="1" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v/>
       </c>
       <c r="BR33" s="1" t="str">
@@ -13646,25 +13278,14 @@
       </c>
     </row>
     <row r="34" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="34">
-        <v>1</v>
-      </c>
-      <c r="C34" s="31">
-        <v>45941</v>
-      </c>
-      <c r="D34" s="31">
-        <v>45941</v>
-      </c>
-      <c r="E34" s="9">
-        <f>COUNT($G34:$DE34)</f>
-        <v>1</v>
-      </c>
-      <c r="F34" s="24" t="s">
-        <v>26</v>
-      </c>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="25"/>
       <c r="G34" s="1" t="str">
         <f t="shared" si="95"/>
         <v/>
@@ -13794,67 +13415,67 @@
         <v/>
       </c>
       <c r="AM34" s="1" t="str">
-        <f t="shared" ref="AM34:BB44" si="100">IF(AND(AM$5&gt;=$C34,AM$5&lt;=$D34),1,"")</f>
+        <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="AN34" s="1" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="AO34" s="1" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="AP34" s="1" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="AQ34" s="1" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="AR34" s="1" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="AS34" s="1" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="AT34" s="1" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="AU34" s="1" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="AV34" s="1" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="AW34" s="1" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="AX34" s="1" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="AY34" s="1" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="AZ34" s="1" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="BA34" s="1" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="BB34" s="1" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" ref="BB34:BQ46" si="99">IF(AND(BB$5&gt;=$C34,BB$5&lt;=$D34),1,"")</f>
         <v/>
       </c>
       <c r="BC34" s="1" t="str">
@@ -13881,435 +13502,443 @@
         <f t="shared" si="99"/>
         <v/>
       </c>
-      <c r="BI34" s="1">
+      <c r="BI34" s="1" t="str">
+        <f t="shared" si="99"/>
+        <v/>
+      </c>
+      <c r="BJ34" s="1" t="str">
+        <f t="shared" si="99"/>
+        <v/>
+      </c>
+      <c r="BK34" s="1" t="str">
+        <f t="shared" si="99"/>
+        <v/>
+      </c>
+      <c r="BL34" s="1" t="str">
+        <f t="shared" si="99"/>
+        <v/>
+      </c>
+      <c r="BM34" s="1" t="str">
+        <f t="shared" si="99"/>
+        <v/>
+      </c>
+      <c r="BN34" s="1" t="str">
+        <f t="shared" si="99"/>
+        <v/>
+      </c>
+      <c r="BO34" s="1" t="str">
+        <f t="shared" si="99"/>
+        <v/>
+      </c>
+      <c r="BP34" s="1" t="str">
+        <f t="shared" si="99"/>
+        <v/>
+      </c>
+      <c r="BQ34" s="1" t="str">
+        <f t="shared" si="99"/>
+        <v/>
+      </c>
+      <c r="BR34" s="1" t="str">
+        <f t="shared" si="92"/>
+        <v/>
+      </c>
+      <c r="BS34" s="1" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="BT34" s="1" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="BU34" s="1" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="BV34" s="1" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="BW34" s="1" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="BX34" s="1" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="BY34" s="1" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="BZ34" s="1" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="CA34" s="1" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="CB34" s="1" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="CC34" s="1" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="CD34" s="1" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="CE34" s="1" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="CF34" s="1" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="CG34" s="1" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="CH34" s="1" t="str">
+        <f t="shared" si="98"/>
+        <v/>
+      </c>
+      <c r="CI34" s="1" t="str">
+        <f t="shared" si="98"/>
+        <v/>
+      </c>
+      <c r="CJ34" s="1" t="str">
+        <f t="shared" si="98"/>
+        <v/>
+      </c>
+      <c r="CK34" s="1" t="str">
+        <f t="shared" si="98"/>
+        <v/>
+      </c>
+      <c r="CL34" s="1" t="str">
+        <f t="shared" si="98"/>
+        <v/>
+      </c>
+      <c r="CM34" s="1" t="str">
+        <f t="shared" si="98"/>
+        <v/>
+      </c>
+      <c r="CN34" s="1" t="str">
+        <f t="shared" si="98"/>
+        <v/>
+      </c>
+      <c r="CO34" s="1" t="str">
+        <f t="shared" si="98"/>
+        <v/>
+      </c>
+      <c r="CP34" s="1" t="str">
+        <f t="shared" si="98"/>
+        <v/>
+      </c>
+      <c r="CQ34" s="1" t="str">
+        <f t="shared" si="98"/>
+        <v/>
+      </c>
+      <c r="CR34" s="1" t="str">
+        <f t="shared" si="98"/>
+        <v/>
+      </c>
+      <c r="CS34" s="1" t="str">
+        <f t="shared" si="98"/>
+        <v/>
+      </c>
+      <c r="CT34" s="1" t="str">
+        <f t="shared" si="98"/>
+        <v/>
+      </c>
+      <c r="CU34" s="1" t="str">
+        <f t="shared" si="98"/>
+        <v/>
+      </c>
+      <c r="CV34" s="1" t="str">
+        <f t="shared" si="98"/>
+        <v/>
+      </c>
+      <c r="CW34" s="1" t="str">
+        <f t="shared" si="98"/>
+        <v/>
+      </c>
+      <c r="CX34" s="1" t="str">
+        <f t="shared" si="96"/>
+        <v/>
+      </c>
+      <c r="CY34" s="1" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="CZ34" s="1" t="str">
+        <f t="shared" si="86"/>
+        <v/>
+      </c>
+      <c r="DA34" s="1" t="str">
+        <f t="shared" si="86"/>
+        <v/>
+      </c>
+      <c r="DB34" s="1" t="str">
+        <f t="shared" si="86"/>
+        <v/>
+      </c>
+      <c r="DC34" s="1" t="str">
+        <f t="shared" si="86"/>
+        <v/>
+      </c>
+      <c r="DD34" s="1" t="str">
+        <f t="shared" si="86"/>
+        <v/>
+      </c>
+      <c r="DE34" s="1" t="str">
+        <f t="shared" si="86"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="34">
+        <v>1</v>
+      </c>
+      <c r="C35" s="31">
+        <v>45941</v>
+      </c>
+      <c r="D35" s="31">
+        <v>45941</v>
+      </c>
+      <c r="E35" s="9">
+        <f>COUNT($G35:$DE35)</f>
+        <v>1</v>
+      </c>
+      <c r="F35" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="1" t="str">
+        <f t="shared" si="95"/>
+        <v/>
+      </c>
+      <c r="H35" s="1" t="str">
+        <f t="shared" si="95"/>
+        <v/>
+      </c>
+      <c r="I35" s="1" t="str">
+        <f t="shared" si="95"/>
+        <v/>
+      </c>
+      <c r="J35" s="1" t="str">
+        <f t="shared" si="95"/>
+        <v/>
+      </c>
+      <c r="K35" s="1" t="str">
+        <f t="shared" si="95"/>
+        <v/>
+      </c>
+      <c r="L35" s="1" t="str">
+        <f t="shared" si="95"/>
+        <v/>
+      </c>
+      <c r="M35" s="1" t="str">
+        <f t="shared" si="95"/>
+        <v/>
+      </c>
+      <c r="N35" s="1" t="str">
+        <f t="shared" si="95"/>
+        <v/>
+      </c>
+      <c r="O35" s="1" t="str">
+        <f t="shared" si="95"/>
+        <v/>
+      </c>
+      <c r="P35" s="1" t="str">
+        <f t="shared" si="95"/>
+        <v/>
+      </c>
+      <c r="Q35" s="1" t="str">
+        <f t="shared" si="95"/>
+        <v/>
+      </c>
+      <c r="R35" s="1" t="str">
+        <f t="shared" si="95"/>
+        <v/>
+      </c>
+      <c r="S35" s="1" t="str">
+        <f t="shared" si="95"/>
+        <v/>
+      </c>
+      <c r="T35" s="1" t="str">
+        <f t="shared" si="95"/>
+        <v/>
+      </c>
+      <c r="U35" s="1" t="str">
+        <f t="shared" si="95"/>
+        <v/>
+      </c>
+      <c r="V35" s="1" t="str">
+        <f t="shared" si="95"/>
+        <v/>
+      </c>
+      <c r="W35" s="1" t="str">
+        <f t="shared" si="94"/>
+        <v/>
+      </c>
+      <c r="X35" s="1" t="str">
+        <f t="shared" si="94"/>
+        <v/>
+      </c>
+      <c r="Y35" s="1" t="str">
+        <f t="shared" si="94"/>
+        <v/>
+      </c>
+      <c r="Z35" s="1" t="str">
+        <f t="shared" si="94"/>
+        <v/>
+      </c>
+      <c r="AA35" s="1" t="str">
+        <f t="shared" si="94"/>
+        <v/>
+      </c>
+      <c r="AB35" s="1" t="str">
+        <f t="shared" si="94"/>
+        <v/>
+      </c>
+      <c r="AC35" s="1" t="str">
+        <f t="shared" si="94"/>
+        <v/>
+      </c>
+      <c r="AD35" s="1" t="str">
+        <f t="shared" si="94"/>
+        <v/>
+      </c>
+      <c r="AE35" s="1" t="str">
+        <f t="shared" si="94"/>
+        <v/>
+      </c>
+      <c r="AF35" s="1" t="str">
+        <f t="shared" si="94"/>
+        <v/>
+      </c>
+      <c r="AG35" s="1" t="str">
+        <f t="shared" si="94"/>
+        <v/>
+      </c>
+      <c r="AH35" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="AI35" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="AJ35" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="AK35" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="AL35" s="1" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="AM35" s="1" t="str">
+        <f t="shared" ref="AM35:BB46" si="100">IF(AND(AM$5&gt;=$C35,AM$5&lt;=$D35),1,"")</f>
+        <v/>
+      </c>
+      <c r="AN35" s="1" t="str">
+        <f t="shared" si="100"/>
+        <v/>
+      </c>
+      <c r="AO35" s="1" t="str">
+        <f t="shared" si="100"/>
+        <v/>
+      </c>
+      <c r="AP35" s="1" t="str">
+        <f t="shared" si="100"/>
+        <v/>
+      </c>
+      <c r="AQ35" s="1" t="str">
+        <f t="shared" si="100"/>
+        <v/>
+      </c>
+      <c r="AR35" s="1" t="str">
+        <f t="shared" si="100"/>
+        <v/>
+      </c>
+      <c r="AS35" s="1" t="str">
+        <f t="shared" si="100"/>
+        <v/>
+      </c>
+      <c r="AT35" s="1" t="str">
+        <f t="shared" si="100"/>
+        <v/>
+      </c>
+      <c r="AU35" s="1" t="str">
+        <f t="shared" si="100"/>
+        <v/>
+      </c>
+      <c r="AV35" s="1" t="str">
+        <f t="shared" si="100"/>
+        <v/>
+      </c>
+      <c r="AW35" s="1" t="str">
+        <f t="shared" si="100"/>
+        <v/>
+      </c>
+      <c r="AX35" s="1" t="str">
+        <f t="shared" si="100"/>
+        <v/>
+      </c>
+      <c r="AY35" s="1" t="str">
+        <f t="shared" si="100"/>
+        <v/>
+      </c>
+      <c r="AZ35" s="1" t="str">
+        <f t="shared" si="100"/>
+        <v/>
+      </c>
+      <c r="BA35" s="1" t="str">
+        <f t="shared" si="100"/>
+        <v/>
+      </c>
+      <c r="BB35" s="1" t="str">
+        <f t="shared" si="100"/>
+        <v/>
+      </c>
+      <c r="BC35" s="1" t="str">
+        <f t="shared" si="99"/>
+        <v/>
+      </c>
+      <c r="BD35" s="1" t="str">
+        <f t="shared" si="99"/>
+        <v/>
+      </c>
+      <c r="BE35" s="1" t="str">
+        <f t="shared" si="99"/>
+        <v/>
+      </c>
+      <c r="BF35" s="1" t="str">
+        <f t="shared" si="99"/>
+        <v/>
+      </c>
+      <c r="BG35" s="1" t="str">
+        <f t="shared" si="99"/>
+        <v/>
+      </c>
+      <c r="BH35" s="1" t="str">
+        <f t="shared" si="99"/>
+        <v/>
+      </c>
+      <c r="BI35" s="1">
         <f t="shared" si="99"/>
         <v>1</v>
       </c>
-      <c r="BJ34" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BK34" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BL34" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BM34" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BN34" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BO34" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BP34" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BQ34" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BR34" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BS34" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BT34" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BU34" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BV34" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BW34" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BX34" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BY34" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BZ34" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="CA34" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="CB34" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="CC34" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="CD34" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="CE34" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="CF34" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="CG34" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="CH34" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CI34" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CJ34" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CK34" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CL34" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CM34" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CN34" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CO34" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CP34" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CQ34" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CR34" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CS34" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CT34" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CU34" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CV34" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CW34" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CX34" s="1" t="str">
-        <f t="shared" si="96"/>
-        <v/>
-      </c>
-      <c r="CY34" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CZ34" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-      <c r="DA34" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-      <c r="DB34" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-      <c r="DC34" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-      <c r="DD34" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-      <c r="DE34" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="11"/>
-      <c r="B35" s="34">
-        <v>0</v>
-      </c>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="9">
-        <f t="shared" ref="E35" si="101">COUNT($G35:$DE35)</f>
-        <v>0</v>
-      </c>
-      <c r="F35" s="24"/>
-      <c r="G35" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="H35" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="I35" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="J35" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="K35" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="L35" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="M35" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="N35" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="O35" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="P35" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="Q35" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="R35" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="S35" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="T35" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="U35" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="V35" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="W35" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="X35" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="Y35" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="Z35" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="AA35" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="AB35" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="AC35" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="AD35" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="AE35" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="AF35" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="AG35" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="AH35" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AI35" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AJ35" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AK35" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AL35" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AM35" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AN35" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AO35" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AP35" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AQ35" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AR35" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AS35" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AT35" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AU35" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AV35" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AW35" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AX35" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AY35" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AZ35" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="BA35" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="BB35" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="BC35" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BD35" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BE35" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BF35" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BG35" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BH35" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BI35" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
       <c r="BJ35" s="1" t="str">
         <f t="shared" si="99"/>
         <v/>
@@ -14503,448 +14132,26 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:109" x14ac:dyDescent="0.45">
-      <c r="A36" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="H36" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="I36" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="J36" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="K36" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="L36" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="M36" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="N36" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="O36" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="P36" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="Q36" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="R36" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="S36" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="T36" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="U36" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="V36" s="1" t="str">
-        <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="W36" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="X36" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="Y36" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="Z36" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="AA36" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="AB36" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="AC36" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="AD36" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="AE36" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="AF36" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="AG36" s="1" t="str">
-        <f t="shared" si="94"/>
-        <v/>
-      </c>
-      <c r="AH36" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AI36" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AJ36" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AK36" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AL36" s="1" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="AM36" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AN36" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AO36" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AP36" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AQ36" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AR36" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AS36" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AT36" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AU36" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AV36" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AW36" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AX36" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AY36" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AZ36" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="BA36" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="BB36" s="1" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="BC36" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BD36" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BE36" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BF36" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BG36" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BH36" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BI36" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BJ36" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BK36" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BL36" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BM36" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BN36" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BO36" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BP36" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BQ36" s="1" t="str">
-        <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BR36" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BS36" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BT36" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BU36" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BV36" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BW36" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BX36" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BY36" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BZ36" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="CA36" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="CB36" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="CC36" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="CD36" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="CE36" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="CF36" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="CG36" s="1" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="CH36" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CI36" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CJ36" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CK36" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CL36" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CM36" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CN36" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CO36" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CP36" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CQ36" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CR36" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CS36" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CT36" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CU36" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CV36" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CW36" s="1" t="str">
-        <f t="shared" si="98"/>
-        <v/>
-      </c>
-      <c r="CX36" s="1" t="str">
-        <f t="shared" si="96"/>
-        <v/>
-      </c>
-      <c r="CY36" s="1" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="CZ36" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-      <c r="DA36" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-      <c r="DB36" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-      <c r="DC36" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-      <c r="DD36" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
-      <c r="DE36" s="1" t="str">
-        <f t="shared" si="86"/>
-        <v/>
-      </c>
+    <row r="36" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="11"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="24"/>
     </row>
-    <row r="37" spans="1:109" x14ac:dyDescent="0.45">
-      <c r="A37" s="11" t="s">
-        <v>33</v>
-      </c>
+    <row r="37" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="11"/>
       <c r="B37" s="34">
-        <v>0.7</v>
-      </c>
-      <c r="C37" s="31">
-        <v>45947</v>
-      </c>
-      <c r="D37" s="31">
-        <v>45952</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
       <c r="E37" s="9">
-        <f>COUNT($G37:$DE37)</f>
-        <v>6</v>
-      </c>
-      <c r="F37" s="24" t="s">
-        <v>27</v>
-      </c>
+        <f t="shared" ref="E37" si="101">COUNT($G37:$DE37)</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="24"/>
       <c r="G37" s="1" t="str">
         <f t="shared" si="95"/>
         <v/>
@@ -15185,29 +14392,29 @@
         <f t="shared" si="99"/>
         <v/>
       </c>
-      <c r="BO37" s="1">
+      <c r="BO37" s="1" t="str">
         <f t="shared" si="99"/>
-        <v>1</v>
-      </c>
-      <c r="BP37" s="1">
+        <v/>
+      </c>
+      <c r="BP37" s="1" t="str">
         <f t="shared" si="99"/>
-        <v>1</v>
-      </c>
-      <c r="BQ37" s="1">
+        <v/>
+      </c>
+      <c r="BQ37" s="1" t="str">
         <f t="shared" si="99"/>
-        <v>1</v>
-      </c>
-      <c r="BR37" s="1">
-        <f t="shared" si="92"/>
-        <v>1</v>
-      </c>
-      <c r="BS37" s="1">
+        <v/>
+      </c>
+      <c r="BR37" s="1" t="str">
+        <f t="shared" si="92"/>
+        <v/>
+      </c>
+      <c r="BS37" s="1" t="str">
         <f t="shared" si="89"/>
-        <v>1</v>
-      </c>
-      <c r="BT37" s="1">
+        <v/>
+      </c>
+      <c r="BT37" s="1" t="str">
         <f t="shared" si="89"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="BU37" s="1" t="str">
         <f t="shared" si="89"/>
@@ -15359,17 +14566,14 @@
       </c>
     </row>
     <row r="38" spans="1:109" x14ac:dyDescent="0.45">
-      <c r="A38" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B38" s="34"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="9">
-        <f t="shared" ref="E38:E41" si="102">COUNT($G38:$DE38)</f>
-        <v>0</v>
-      </c>
-      <c r="F38" s="24"/>
+      <c r="A38" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="25"/>
       <c r="G38" s="1" t="str">
         <f t="shared" si="95"/>
         <v/>
@@ -15785,20 +14989,24 @@
     </row>
     <row r="39" spans="1:109" x14ac:dyDescent="0.45">
       <c r="A39" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="34"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="34">
+        <v>1</v>
+      </c>
       <c r="C39" s="31">
-        <v>45957</v>
+        <v>45947</v>
       </c>
       <c r="D39" s="31">
-        <v>45960</v>
+        <v>45952</v>
       </c>
       <c r="E39" s="9">
-        <f t="shared" si="102"/>
-        <v>4</v>
-      </c>
-      <c r="F39" s="24"/>
+        <f>COUNT($G39:$DE39)</f>
+        <v>6</v>
+      </c>
+      <c r="F39" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G39" s="1" t="str">
         <f t="shared" si="95"/>
         <v/>
@@ -16039,29 +15247,29 @@
         <f t="shared" si="99"/>
         <v/>
       </c>
-      <c r="BO39" s="1" t="str">
+      <c r="BO39" s="1">
         <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BP39" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="BP39" s="1">
         <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BQ39" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="BQ39" s="1">
         <f t="shared" si="99"/>
-        <v/>
-      </c>
-      <c r="BR39" s="1" t="str">
-        <f t="shared" si="92"/>
-        <v/>
-      </c>
-      <c r="BS39" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="BR39" s="1">
+        <f t="shared" si="92"/>
+        <v>1</v>
+      </c>
+      <c r="BS39" s="1">
         <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BT39" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="BT39" s="1">
         <f t="shared" si="89"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BU39" s="1" t="str">
         <f t="shared" si="89"/>
@@ -16079,21 +15287,21 @@
         <f t="shared" si="89"/>
         <v/>
       </c>
-      <c r="BY39" s="1">
+      <c r="BY39" s="1" t="str">
         <f t="shared" si="89"/>
-        <v>1</v>
-      </c>
-      <c r="BZ39" s="1">
+        <v/>
+      </c>
+      <c r="BZ39" s="1" t="str">
         <f t="shared" si="89"/>
-        <v>1</v>
-      </c>
-      <c r="CA39" s="1">
+        <v/>
+      </c>
+      <c r="CA39" s="1" t="str">
         <f t="shared" si="89"/>
-        <v>1</v>
-      </c>
-      <c r="CB39" s="1">
+        <v/>
+      </c>
+      <c r="CB39" s="1" t="str">
         <f t="shared" si="89"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="CC39" s="1" t="str">
         <f t="shared" si="89"/>
@@ -16213,12 +15421,14 @@
       </c>
     </row>
     <row r="40" spans="1:109" x14ac:dyDescent="0.45">
-      <c r="A40" s="11"/>
+      <c r="A40" s="11" t="s">
+        <v>33</v>
+      </c>
       <c r="B40" s="34"/>
       <c r="C40" s="31"/>
       <c r="D40" s="31"/>
       <c r="E40" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" ref="E40:E43" si="102">COUNT($G40:$DE40)</f>
         <v>0</v>
       </c>
       <c r="F40" s="24"/>
@@ -16636,15 +15846,25 @@
       </c>
     </row>
     <row r="41" spans="1:109" x14ac:dyDescent="0.45">
-      <c r="A41" s="11"/>
-      <c r="B41" s="34"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
+      <c r="A41" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="34">
+        <v>1</v>
+      </c>
+      <c r="C41" s="31">
+        <v>45957</v>
+      </c>
+      <c r="D41" s="31">
+        <v>45960</v>
+      </c>
       <c r="E41" s="9">
         <f t="shared" si="102"/>
-        <v>0</v>
-      </c>
-      <c r="F41" s="24"/>
+        <v>4</v>
+      </c>
+      <c r="F41" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G41" s="1" t="str">
         <f t="shared" si="95"/>
         <v/>
@@ -16706,67 +15926,67 @@
         <v/>
       </c>
       <c r="V41" s="1" t="str">
-        <f t="shared" ref="V41:AK44" si="103">IF(AND(V$5&gt;=$C41,V$5&lt;=$D41),1,"")</f>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="W41" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="X41" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="Y41" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="Z41" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="AA41" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="AB41" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="AC41" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="AD41" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="AE41" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="AF41" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="AG41" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="AH41" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="AI41" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="AJ41" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="AK41" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="AL41" s="1" t="str">
@@ -16925,21 +16145,21 @@
         <f t="shared" si="89"/>
         <v/>
       </c>
-      <c r="BY41" s="1" t="str">
+      <c r="BY41" s="1">
         <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BZ41" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="BZ41" s="1">
         <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="CA41" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="CA41" s="1">
         <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="CB41" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="CB41" s="1">
         <f t="shared" si="89"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CC41" s="1" t="str">
         <f t="shared" si="89"/>
@@ -17030,165 +16250,166 @@
         <v/>
       </c>
       <c r="CY41" s="1" t="str">
-        <f t="shared" ref="CY41:DE41" si="104">IF(AND(CY$5&gt;=$C41,CY$5&lt;=$D41),1,"")</f>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="CZ41" s="1" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="DA41" s="1" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="DB41" s="1" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="DC41" s="1" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="DD41" s="1" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="DE41" s="1" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
     </row>
     <row r="42" spans="1:109" x14ac:dyDescent="0.45">
-      <c r="A42" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="25"/>
+      <c r="A42" s="11"/>
+      <c r="B42" s="34"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="9">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="24"/>
       <c r="G42" s="1" t="str">
-        <f t="shared" ref="G42:V57" si="105">IF(AND(G$5&gt;=$C42,G$5&lt;=$D42),1,"")</f>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="H42" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="I42" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="J42" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="K42" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="L42" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="M42" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="N42" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="O42" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="P42" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="Q42" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="R42" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="S42" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="T42" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="U42" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="V42" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="W42" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="X42" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="Y42" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="Z42" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="AA42" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="AB42" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="AC42" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="AD42" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="AE42" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="AF42" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="AG42" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="AH42" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="AI42" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="AJ42" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="AK42" s="1" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="AL42" s="1" t="str">
@@ -17444,124 +16665,114 @@
         <v/>
       </c>
       <c r="CW42" s="1" t="str">
-        <f t="shared" ref="CW42:DE57" si="106">IF(AND(CW$5&gt;=$C42,CW$5&lt;=$D42),1,"")</f>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CX42" s="1" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="96"/>
         <v/>
       </c>
       <c r="CY42" s="1" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="CZ42" s="1" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="DA42" s="1" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="DB42" s="1" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="DC42" s="1" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="DD42" s="1" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="DE42" s="1" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
     </row>
     <row r="43" spans="1:109" x14ac:dyDescent="0.45">
-      <c r="A43" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B43" s="34">
-        <v>1</v>
-      </c>
-      <c r="C43" s="31">
-        <v>45930</v>
-      </c>
-      <c r="D43" s="31">
-        <v>45945</v>
-      </c>
+      <c r="A43" s="11"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
       <c r="E43" s="9">
-        <f>COUNT($G43:$DE43)</f>
-        <v>16</v>
-      </c>
-      <c r="F43" s="24" t="s">
-        <v>26</v>
-      </c>
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="24"/>
       <c r="G43" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="H43" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="I43" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="J43" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="K43" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="L43" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="M43" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="N43" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="O43" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="P43" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="Q43" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="R43" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="S43" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="T43" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="U43" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="V43" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" ref="V43:AK46" si="103">IF(AND(V$5&gt;=$C43,V$5&lt;=$D43),1,"")</f>
         <v/>
       </c>
       <c r="W43" s="1" t="str">
@@ -17672,69 +16883,69 @@
         <f t="shared" si="100"/>
         <v/>
       </c>
-      <c r="AX43" s="1">
+      <c r="AX43" s="1" t="str">
         <f t="shared" si="100"/>
-        <v>1</v>
-      </c>
-      <c r="AY43" s="1">
+        <v/>
+      </c>
+      <c r="AY43" s="1" t="str">
         <f t="shared" si="100"/>
-        <v>1</v>
-      </c>
-      <c r="AZ43" s="1">
+        <v/>
+      </c>
+      <c r="AZ43" s="1" t="str">
         <f t="shared" si="100"/>
-        <v>1</v>
-      </c>
-      <c r="BA43" s="1">
+        <v/>
+      </c>
+      <c r="BA43" s="1" t="str">
         <f t="shared" si="100"/>
-        <v>1</v>
-      </c>
-      <c r="BB43" s="1">
+        <v/>
+      </c>
+      <c r="BB43" s="1" t="str">
         <f t="shared" si="100"/>
-        <v>1</v>
-      </c>
-      <c r="BC43" s="1">
+        <v/>
+      </c>
+      <c r="BC43" s="1" t="str">
         <f t="shared" si="99"/>
-        <v>1</v>
-      </c>
-      <c r="BD43" s="1">
+        <v/>
+      </c>
+      <c r="BD43" s="1" t="str">
         <f t="shared" si="99"/>
-        <v>1</v>
-      </c>
-      <c r="BE43" s="1">
+        <v/>
+      </c>
+      <c r="BE43" s="1" t="str">
         <f t="shared" si="99"/>
-        <v>1</v>
-      </c>
-      <c r="BF43" s="1">
+        <v/>
+      </c>
+      <c r="BF43" s="1" t="str">
         <f t="shared" si="99"/>
-        <v>1</v>
-      </c>
-      <c r="BG43" s="1">
+        <v/>
+      </c>
+      <c r="BG43" s="1" t="str">
         <f t="shared" si="99"/>
-        <v>1</v>
-      </c>
-      <c r="BH43" s="1">
+        <v/>
+      </c>
+      <c r="BH43" s="1" t="str">
         <f t="shared" si="99"/>
-        <v>1</v>
-      </c>
-      <c r="BI43" s="1">
+        <v/>
+      </c>
+      <c r="BI43" s="1" t="str">
         <f t="shared" si="99"/>
-        <v>1</v>
-      </c>
-      <c r="BJ43" s="1">
+        <v/>
+      </c>
+      <c r="BJ43" s="1" t="str">
         <f t="shared" si="99"/>
-        <v>1</v>
-      </c>
-      <c r="BK43" s="1">
+        <v/>
+      </c>
+      <c r="BK43" s="1" t="str">
         <f t="shared" si="99"/>
-        <v>1</v>
-      </c>
-      <c r="BL43" s="1">
+        <v/>
+      </c>
+      <c r="BL43" s="1" t="str">
         <f t="shared" si="99"/>
-        <v>1</v>
-      </c>
-      <c r="BM43" s="1">
+        <v/>
+      </c>
+      <c r="BM43" s="1" t="str">
         <f t="shared" si="99"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="BN43" s="1" t="str">
         <f t="shared" si="99"/>
@@ -17761,180 +16972,169 @@
         <v/>
       </c>
       <c r="BT43" s="1" t="str">
-        <f t="shared" ref="BT43:CI57" si="107">IF(AND(BT$5&gt;=$C43,BT$5&lt;=$D43),1,"")</f>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BU43" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BV43" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BW43" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BX43" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BY43" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BZ43" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="CA43" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="CB43" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="CC43" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="CD43" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="CE43" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="CF43" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="CG43" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="CH43" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CI43" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CJ43" s="1" t="str">
-        <f t="shared" ref="CJ43:CY57" si="108">IF(AND(CJ$5&gt;=$C43,CJ$5&lt;=$D43),1,"")</f>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CK43" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CL43" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CM43" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CN43" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CO43" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CP43" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CQ43" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CR43" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CS43" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CT43" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CU43" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CV43" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CW43" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CX43" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="96"/>
         <v/>
       </c>
       <c r="CY43" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" ref="CY43:DE43" si="104">IF(AND(CY$5&gt;=$C43,CY$5&lt;=$D43),1,"")</f>
         <v/>
       </c>
       <c r="CZ43" s="1" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="DA43" s="1" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="DB43" s="1" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="DC43" s="1" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="DD43" s="1" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="DE43" s="1" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v/>
       </c>
     </row>
     <row r="44" spans="1:109" x14ac:dyDescent="0.45">
-      <c r="A44" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B44" s="34">
-        <v>1</v>
-      </c>
-      <c r="C44" s="31">
-        <v>45900</v>
-      </c>
-      <c r="D44" s="31">
-        <v>45906</v>
-      </c>
-      <c r="E44" s="9">
-        <f>COUNT($G49:$DE49)</f>
-        <v>7</v>
-      </c>
-      <c r="F44" s="24" t="s">
-        <v>26</v>
-      </c>
+      <c r="A44" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="25"/>
       <c r="G44" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" ref="G44:V59" si="105">IF(AND(G$5&gt;=$C44,G$5&lt;=$D44),1,"")</f>
         <v/>
       </c>
       <c r="H44" s="1" t="str">
@@ -17985,33 +17185,33 @@
         <f t="shared" si="105"/>
         <v/>
       </c>
-      <c r="T44" s="1">
+      <c r="T44" s="1" t="str">
         <f t="shared" si="105"/>
-        <v>1</v>
-      </c>
-      <c r="U44" s="1">
+        <v/>
+      </c>
+      <c r="U44" s="1" t="str">
         <f t="shared" si="105"/>
-        <v>1</v>
-      </c>
-      <c r="V44" s="1">
+        <v/>
+      </c>
+      <c r="V44" s="1" t="str">
         <f t="shared" si="105"/>
-        <v>1</v>
-      </c>
-      <c r="W44" s="1">
+        <v/>
+      </c>
+      <c r="W44" s="1" t="str">
         <f t="shared" si="103"/>
-        <v>1</v>
-      </c>
-      <c r="X44" s="1">
+        <v/>
+      </c>
+      <c r="X44" s="1" t="str">
         <f t="shared" si="103"/>
-        <v>1</v>
-      </c>
-      <c r="Y44" s="1">
+        <v/>
+      </c>
+      <c r="Y44" s="1" t="str">
         <f t="shared" si="103"/>
-        <v>1</v>
-      </c>
-      <c r="Z44" s="1">
+        <v/>
+      </c>
+      <c r="Z44" s="1" t="str">
         <f t="shared" si="103"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AA44" s="1" t="str">
         <f t="shared" si="103"/>
@@ -18190,135 +17390,135 @@
         <v/>
       </c>
       <c r="BS44" s="1" t="str">
-        <f t="shared" ref="H44:BS48" si="109">IF(AND(BS$5&gt;=$C44,BS$5&lt;=$D44),1,"")</f>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BT44" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BU44" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BV44" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BW44" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BX44" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BY44" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BZ44" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="CA44" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="CB44" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="CC44" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="CD44" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="CE44" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="CF44" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="CG44" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="CH44" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CI44" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CJ44" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CK44" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CL44" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CM44" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CN44" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CO44" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CP44" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CQ44" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CR44" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CS44" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CT44" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CU44" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CV44" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="CW44" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" ref="CW44:DE59" si="106">IF(AND(CW$5&gt;=$C44,CW$5&lt;=$D44),1,"")</f>
         <v/>
       </c>
       <c r="CX44" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="106"/>
         <v/>
       </c>
       <c r="CY44" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="106"/>
         <v/>
       </c>
       <c r="CZ44" s="1" t="str">
@@ -18348,282 +17548,286 @@
     </row>
     <row r="45" spans="1:109" x14ac:dyDescent="0.45">
       <c r="A45" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="34"/>
+        <v>24</v>
+      </c>
+      <c r="B45" s="34">
+        <v>1</v>
+      </c>
       <c r="C45" s="31">
-        <v>45964</v>
+        <v>45930</v>
       </c>
       <c r="D45" s="31">
-        <v>45965</v>
+        <v>45945</v>
       </c>
       <c r="E45" s="9">
         <f>COUNT($G45:$DE45)</f>
-        <v>2</v>
-      </c>
-      <c r="F45" s="24"/>
+        <v>16</v>
+      </c>
+      <c r="F45" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G45" s="1" t="str">
         <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="H45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="I45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="J45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="K45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="L45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="M45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="N45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="O45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="P45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="Q45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="R45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="S45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="T45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="U45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="V45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="W45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="X45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="Y45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="Z45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AA45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AB45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AC45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AD45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AE45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AF45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AG45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AH45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AI45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AJ45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AK45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AL45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="AM45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AN45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AO45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AP45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AQ45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AR45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AS45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AT45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AU45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AV45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AW45" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="AX45" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="AY45" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="AZ45" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="BA45" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="BB45" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="BC45" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="BD45" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="BE45" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="BF45" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="BG45" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="BH45" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="BI45" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="BJ45" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="BK45" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="BL45" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="BM45" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
+        <f t="shared" si="100"/>
+        <v/>
+      </c>
+      <c r="AX45" s="1">
+        <f t="shared" si="100"/>
+        <v>1</v>
+      </c>
+      <c r="AY45" s="1">
+        <f t="shared" si="100"/>
+        <v>1</v>
+      </c>
+      <c r="AZ45" s="1">
+        <f t="shared" si="100"/>
+        <v>1</v>
+      </c>
+      <c r="BA45" s="1">
+        <f t="shared" si="100"/>
+        <v>1</v>
+      </c>
+      <c r="BB45" s="1">
+        <f t="shared" si="100"/>
+        <v>1</v>
+      </c>
+      <c r="BC45" s="1">
+        <f t="shared" si="99"/>
+        <v>1</v>
+      </c>
+      <c r="BD45" s="1">
+        <f t="shared" si="99"/>
+        <v>1</v>
+      </c>
+      <c r="BE45" s="1">
+        <f t="shared" si="99"/>
+        <v>1</v>
+      </c>
+      <c r="BF45" s="1">
+        <f t="shared" si="99"/>
+        <v>1</v>
+      </c>
+      <c r="BG45" s="1">
+        <f t="shared" si="99"/>
+        <v>1</v>
+      </c>
+      <c r="BH45" s="1">
+        <f t="shared" si="99"/>
+        <v>1</v>
+      </c>
+      <c r="BI45" s="1">
+        <f t="shared" si="99"/>
+        <v>1</v>
+      </c>
+      <c r="BJ45" s="1">
+        <f t="shared" si="99"/>
+        <v>1</v>
+      </c>
+      <c r="BK45" s="1">
+        <f t="shared" si="99"/>
+        <v>1</v>
+      </c>
+      <c r="BL45" s="1">
+        <f t="shared" si="99"/>
+        <v>1</v>
+      </c>
+      <c r="BM45" s="1">
+        <f t="shared" si="99"/>
+        <v>1</v>
       </c>
       <c r="BN45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="BO45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="BP45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="BQ45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="BR45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="92"/>
         <v/>
       </c>
       <c r="BS45" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BT45" s="1" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" ref="BT45:CI59" si="107">IF(AND(BT$5&gt;=$C45,BT$5&lt;=$D45),1,"")</f>
         <v/>
       </c>
       <c r="BU45" s="1" t="str">
@@ -18670,13 +17874,13 @@
         <f t="shared" si="107"/>
         <v/>
       </c>
-      <c r="CF45" s="38">
+      <c r="CF45" s="1" t="str">
         <f t="shared" si="107"/>
-        <v>1</v>
-      </c>
-      <c r="CG45" s="38">
+        <v/>
+      </c>
+      <c r="CG45" s="1" t="str">
         <f t="shared" si="107"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="CH45" s="1" t="str">
         <f t="shared" si="107"/>
@@ -18687,7 +17891,7 @@
         <v/>
       </c>
       <c r="CJ45" s="1" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" ref="CJ45:CY59" si="108">IF(AND(CJ$5&gt;=$C45,CJ$5&lt;=$D45),1,"")</f>
         <v/>
       </c>
       <c r="CK45" s="1" t="str">
@@ -18776,273 +17980,283 @@
       </c>
     </row>
     <row r="46" spans="1:109" x14ac:dyDescent="0.45">
-      <c r="A46" s="11"/>
-      <c r="B46" s="34"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
+      <c r="A46" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" s="34">
+        <v>1</v>
+      </c>
+      <c r="C46" s="31">
+        <v>45900</v>
+      </c>
+      <c r="D46" s="31">
+        <v>45906</v>
+      </c>
       <c r="E46" s="9">
-        <f>COUNT($G46:$DE46)</f>
-        <v>0</v>
-      </c>
-      <c r="F46" s="24"/>
+        <f>COUNT($G51:$DE51)</f>
+        <v>7</v>
+      </c>
+      <c r="F46" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G46" s="1" t="str">
         <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="H46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="I46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="J46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="K46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="L46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="M46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="N46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="O46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="P46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="Q46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="R46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="S46" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="T46" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="U46" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="V46" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="W46" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="X46" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="Y46" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
-      </c>
-      <c r="Z46" s="1" t="str">
-        <f t="shared" si="109"/>
-        <v/>
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="T46" s="1">
+        <f t="shared" si="105"/>
+        <v>1</v>
+      </c>
+      <c r="U46" s="1">
+        <f t="shared" si="105"/>
+        <v>1</v>
+      </c>
+      <c r="V46" s="1">
+        <f t="shared" si="105"/>
+        <v>1</v>
+      </c>
+      <c r="W46" s="1">
+        <f t="shared" si="103"/>
+        <v>1</v>
+      </c>
+      <c r="X46" s="1">
+        <f t="shared" si="103"/>
+        <v>1</v>
+      </c>
+      <c r="Y46" s="1">
+        <f t="shared" si="103"/>
+        <v>1</v>
+      </c>
+      <c r="Z46" s="1">
+        <f t="shared" si="103"/>
+        <v>1</v>
       </c>
       <c r="AA46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AB46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AC46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AD46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AE46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AF46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AG46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AH46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AI46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AJ46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AK46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="AL46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="AM46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AN46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AO46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AP46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AQ46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AR46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AS46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AT46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AU46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AV46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AW46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AX46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AY46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="AZ46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="BA46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="BB46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="BC46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="BD46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="BE46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="BF46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="BG46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="BH46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="BI46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="BJ46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="BK46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="BL46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="BM46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="BN46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="BO46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="BP46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="BQ46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="BR46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="92"/>
         <v/>
       </c>
       <c r="BS46" s="1" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" ref="H46:BS50" si="109">IF(AND(BS$5&gt;=$C46,BS$5&lt;=$D46),1,"")</f>
         <v/>
       </c>
       <c r="BT46" s="1" t="str">
@@ -19199,13 +18413,19 @@
       </c>
     </row>
     <row r="47" spans="1:109" x14ac:dyDescent="0.45">
-      <c r="A47" s="11"/>
+      <c r="A47" s="11" t="s">
+        <v>37</v>
+      </c>
       <c r="B47" s="34"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
+      <c r="C47" s="31">
+        <v>45964</v>
+      </c>
+      <c r="D47" s="31">
+        <v>45965</v>
+      </c>
       <c r="E47" s="9">
-        <f>COUNT(#REF!)</f>
-        <v>0</v>
+        <f>COUNT($G47:$DE47)</f>
+        <v>2</v>
       </c>
       <c r="F47" s="24"/>
       <c r="G47" s="1" t="str">
@@ -19516,13 +18736,13 @@
         <f t="shared" si="107"/>
         <v/>
       </c>
-      <c r="CF47" s="1" t="str">
+      <c r="CF47" s="37">
         <f t="shared" si="107"/>
-        <v/>
-      </c>
-      <c r="CG47" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="CG47" s="37">
         <f t="shared" si="107"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CH47" s="1" t="str">
         <f t="shared" si="107"/>
@@ -19622,14 +18842,15 @@
       </c>
     </row>
     <row r="48" spans="1:109" x14ac:dyDescent="0.45">
-      <c r="A48" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="25"/>
+      <c r="A48" s="11"/>
+      <c r="B48" s="34"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="9">
+        <f>COUNT($G48:$DE48)</f>
+        <v>0</v>
+      </c>
+      <c r="F48" s="24"/>
       <c r="G48" s="1" t="str">
         <f t="shared" si="105"/>
         <v/>
@@ -19883,11 +19104,11 @@
         <v/>
       </c>
       <c r="BR48" s="1" t="str">
-        <f t="shared" ref="BR48:BS58" si="110">IF(AND(BR$5&gt;=$C48,BR$5&lt;=$D48),1,"")</f>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BS48" s="1" t="str">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BT48" s="1" t="str">
@@ -20044,21 +19265,13 @@
       </c>
     </row>
     <row r="49" spans="1:109" x14ac:dyDescent="0.45">
-      <c r="A49" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="34">
+      <c r="A49" s="11"/>
+      <c r="B49" s="34"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="9">
+        <f>COUNT(#REF!)</f>
         <v>0</v>
-      </c>
-      <c r="C49" s="31">
-        <v>45966</v>
-      </c>
-      <c r="D49" s="31">
-        <v>45972</v>
-      </c>
-      <c r="E49" s="9">
-        <f>COUNT($G49:$DE49)</f>
-        <v>7</v>
       </c>
       <c r="F49" s="24"/>
       <c r="G49" s="1" t="str">
@@ -20066,259 +19279,259 @@
         <v/>
       </c>
       <c r="H49" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="I49" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="J49" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="K49" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="L49" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="M49" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="N49" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="O49" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="P49" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="Q49" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="R49" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="S49" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="T49" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="U49" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="V49" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="W49" s="1" t="str">
-        <f t="shared" ref="W49:AL58" si="111">IF(AND(W$5&gt;=$C49,W$5&lt;=$D49),1,"")</f>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="X49" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="Y49" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="Z49" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AA49" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AB49" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AC49" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AD49" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AE49" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AF49" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AG49" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AH49" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AI49" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AJ49" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AK49" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AL49" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AM49" s="1" t="str">
-        <f t="shared" ref="AM49:BB58" si="112">IF(AND(AM$5&gt;=$C49,AM$5&lt;=$D49),1,"")</f>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AN49" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AO49" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AP49" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AQ49" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AR49" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AS49" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AT49" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AU49" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AV49" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AW49" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AX49" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AY49" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AZ49" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BA49" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BB49" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BC49" s="1" t="str">
-        <f t="shared" ref="BC49:BR58" si="113">IF(AND(BC$5&gt;=$C49,BC$5&lt;=$D49),1,"")</f>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BD49" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BE49" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BF49" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BG49" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BH49" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BI49" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BJ49" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BK49" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BL49" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BM49" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BN49" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BO49" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BP49" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BQ49" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BR49" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BS49" s="1" t="str">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BT49" s="1" t="str">
@@ -20377,35 +19590,35 @@
         <f t="shared" si="107"/>
         <v/>
       </c>
-      <c r="CH49" s="38">
+      <c r="CH49" s="1" t="str">
         <f t="shared" si="107"/>
-        <v>1</v>
-      </c>
-      <c r="CI49" s="38">
+        <v/>
+      </c>
+      <c r="CI49" s="1" t="str">
         <f t="shared" si="107"/>
-        <v>1</v>
-      </c>
-      <c r="CJ49" s="38">
+        <v/>
+      </c>
+      <c r="CJ49" s="1" t="str">
         <f t="shared" si="108"/>
-        <v>1</v>
-      </c>
-      <c r="CK49" s="38">
+        <v/>
+      </c>
+      <c r="CK49" s="1" t="str">
         <f t="shared" si="108"/>
-        <v>1</v>
-      </c>
-      <c r="CL49" s="38">
+        <v/>
+      </c>
+      <c r="CL49" s="1" t="str">
         <f t="shared" si="108"/>
-        <v>1</v>
-      </c>
-      <c r="CM49" s="38">
+        <v/>
+      </c>
+      <c r="CM49" s="1" t="str">
         <f t="shared" si="108"/>
-        <v>1</v>
-      </c>
-      <c r="CN49" s="38">
+        <v/>
+      </c>
+      <c r="CN49" s="1" t="str">
         <f t="shared" si="108"/>
-        <v>1</v>
-      </c>
-      <c r="CO49" s="38" t="str">
+        <v/>
+      </c>
+      <c r="CO49" s="1" t="str">
         <f t="shared" si="108"/>
         <v/>
       </c>
@@ -20475,266 +19688,268 @@
       </c>
     </row>
     <row r="50" spans="1:109" x14ac:dyDescent="0.45">
-      <c r="A50" s="11"/>
-      <c r="B50" s="34"/>
-      <c r="C50" s="31"/>
-      <c r="D50" s="31"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="24"/>
+      <c r="A50" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="25"/>
       <c r="G50" s="1" t="str">
         <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="H50" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="I50" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="J50" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="K50" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="L50" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="M50" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="N50" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="O50" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="P50" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="Q50" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="R50" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="S50" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="T50" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="U50" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="V50" s="1" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="W50" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="X50" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="Y50" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="Z50" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AA50" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AB50" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AC50" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AD50" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AE50" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AF50" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AG50" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AH50" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AI50" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AJ50" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AK50" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AL50" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AM50" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AN50" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AO50" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AP50" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AQ50" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AR50" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AS50" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AT50" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AU50" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AV50" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AW50" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AX50" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AY50" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="AZ50" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BA50" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BB50" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BC50" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BD50" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BE50" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BF50" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BG50" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BH50" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BI50" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BJ50" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BK50" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BL50" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BM50" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BN50" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BO50" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BP50" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BQ50" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="BR50" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" ref="BR50:BS60" si="110">IF(AND(BR$5&gt;=$C50,BR$5&lt;=$D50),1,"")</f>
         <v/>
       </c>
       <c r="BS50" s="1" t="str">
@@ -20895,11 +20110,22 @@
       </c>
     </row>
     <row r="51" spans="1:109" x14ac:dyDescent="0.45">
-      <c r="A51" s="11"/>
-      <c r="B51" s="34"/>
-      <c r="C51" s="31"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="9"/>
+      <c r="A51" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="34">
+        <v>0</v>
+      </c>
+      <c r="C51" s="31">
+        <v>45966</v>
+      </c>
+      <c r="D51" s="31">
+        <v>45972</v>
+      </c>
+      <c r="E51" s="9">
+        <f>COUNT($G51:$DE51)</f>
+        <v>7</v>
+      </c>
       <c r="F51" s="24"/>
       <c r="G51" s="1" t="str">
         <f t="shared" si="105"/>
@@ -20966,7 +20192,7 @@
         <v/>
       </c>
       <c r="W51" s="1" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" ref="W51:AL60" si="111">IF(AND(W$5&gt;=$C51,W$5&lt;=$D51),1,"")</f>
         <v/>
       </c>
       <c r="X51" s="1" t="str">
@@ -21030,7 +20256,7 @@
         <v/>
       </c>
       <c r="AM51" s="1" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" ref="AM51:BB60" si="112">IF(AND(AM$5&gt;=$C51,AM$5&lt;=$D51),1,"")</f>
         <v/>
       </c>
       <c r="AN51" s="1" t="str">
@@ -21094,7 +20320,7 @@
         <v/>
       </c>
       <c r="BC51" s="1" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" ref="BC51:BR60" si="113">IF(AND(BC$5&gt;=$C51,BC$5&lt;=$D51),1,"")</f>
         <v/>
       </c>
       <c r="BD51" s="1" t="str">
@@ -21217,35 +20443,35 @@
         <f t="shared" si="107"/>
         <v/>
       </c>
-      <c r="CH51" s="1" t="str">
+      <c r="CH51" s="37">
         <f t="shared" si="107"/>
-        <v/>
-      </c>
-      <c r="CI51" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="CI51" s="37">
         <f t="shared" si="107"/>
-        <v/>
-      </c>
-      <c r="CJ51" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="CJ51" s="37">
         <f t="shared" si="108"/>
-        <v/>
-      </c>
-      <c r="CK51" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="CK51" s="37">
         <f t="shared" si="108"/>
-        <v/>
-      </c>
-      <c r="CL51" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="CL51" s="37">
         <f t="shared" si="108"/>
-        <v/>
-      </c>
-      <c r="CM51" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="CM51" s="37">
         <f t="shared" si="108"/>
-        <v/>
-      </c>
-      <c r="CN51" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="CN51" s="37">
         <f t="shared" si="108"/>
-        <v/>
-      </c>
-      <c r="CO51" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="CO51" s="37" t="str">
         <f t="shared" si="108"/>
         <v/>
       </c>
@@ -21315,14 +20541,12 @@
       </c>
     </row>
     <row r="52" spans="1:109" x14ac:dyDescent="0.45">
-      <c r="A52" s="39" t="s">
-        <v>47</v>
-      </c>
-      <c r="B52" s="40"/>
-      <c r="C52" s="40"/>
-      <c r="D52" s="40"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="42"/>
+      <c r="A52" s="11"/>
+      <c r="B52" s="34"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="24"/>
       <c r="G52" s="1" t="str">
         <f t="shared" si="105"/>
         <v/>
@@ -21737,14 +20961,12 @@
       </c>
     </row>
     <row r="53" spans="1:109" x14ac:dyDescent="0.45">
-      <c r="A53" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="25"/>
+      <c r="A53" s="11"/>
+      <c r="B53" s="34"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="24"/>
       <c r="G53" s="1" t="str">
         <f t="shared" si="105"/>
         <v/>
@@ -22159,23 +21381,14 @@
       </c>
     </row>
     <row r="54" spans="1:109" x14ac:dyDescent="0.45">
-      <c r="A54" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B54" s="34">
-        <v>0</v>
-      </c>
-      <c r="C54" s="31">
-        <v>45957</v>
-      </c>
-      <c r="D54" s="31">
-        <v>45960</v>
-      </c>
-      <c r="E54" s="9">
-        <f>COUNT($G54:$DE54)</f>
-        <v>4</v>
-      </c>
-      <c r="F54" s="24"/>
+      <c r="A54" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="B54" s="39"/>
+      <c r="C54" s="39"/>
+      <c r="D54" s="39"/>
+      <c r="E54" s="40"/>
+      <c r="F54" s="41"/>
       <c r="G54" s="1" t="str">
         <f t="shared" si="105"/>
         <v/>
@@ -22456,21 +21669,21 @@
         <f t="shared" si="107"/>
         <v/>
       </c>
-      <c r="BY54" s="1">
+      <c r="BY54" s="1" t="str">
         <f t="shared" si="107"/>
-        <v>1</v>
-      </c>
-      <c r="BZ54" s="1">
+        <v/>
+      </c>
+      <c r="BZ54" s="1" t="str">
         <f t="shared" si="107"/>
-        <v>1</v>
-      </c>
-      <c r="CA54" s="1">
+        <v/>
+      </c>
+      <c r="CA54" s="1" t="str">
         <f t="shared" si="107"/>
-        <v>1</v>
-      </c>
-      <c r="CB54" s="1">
+        <v/>
+      </c>
+      <c r="CB54" s="1" t="str">
         <f t="shared" si="107"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="CC54" s="1" t="str">
         <f t="shared" si="107"/>
@@ -22590,15 +21803,14 @@
       </c>
     </row>
     <row r="55" spans="1:109" x14ac:dyDescent="0.45">
-      <c r="A55" s="11"/>
-      <c r="B55" s="34"/>
-      <c r="C55" s="31"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="9">
-        <f>COUNT($G60:$DE60)</f>
-        <v>0</v>
-      </c>
-      <c r="F55" s="24"/>
+      <c r="A55" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="25"/>
       <c r="G55" s="1" t="str">
         <f t="shared" si="105"/>
         <v/>
@@ -23013,13 +22225,21 @@
       </c>
     </row>
     <row r="56" spans="1:109" x14ac:dyDescent="0.45">
-      <c r="A56" s="11"/>
-      <c r="B56" s="34"/>
-      <c r="C56" s="31"/>
-      <c r="D56" s="31"/>
+      <c r="A56" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B56" s="34">
+        <v>0</v>
+      </c>
+      <c r="C56" s="31">
+        <v>45957</v>
+      </c>
+      <c r="D56" s="31">
+        <v>45960</v>
+      </c>
       <c r="E56" s="9">
         <f>COUNT($G56:$DE56)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F56" s="24"/>
       <c r="G56" s="1" t="str">
@@ -23302,21 +22522,21 @@
         <f t="shared" si="107"/>
         <v/>
       </c>
-      <c r="BY56" s="1" t="str">
+      <c r="BY56" s="1">
         <f t="shared" si="107"/>
-        <v/>
-      </c>
-      <c r="BZ56" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="BZ56" s="1">
         <f t="shared" si="107"/>
-        <v/>
-      </c>
-      <c r="CA56" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="CA56" s="1">
         <f t="shared" si="107"/>
-        <v/>
-      </c>
-      <c r="CB56" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="CB56" s="1">
         <f t="shared" si="107"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CC56" s="1" t="str">
         <f t="shared" si="107"/>
@@ -23441,7 +22661,7 @@
       <c r="C57" s="31"/>
       <c r="D57" s="31"/>
       <c r="E57" s="9">
-        <f>COUNT($G57:$DE57)</f>
+        <f>COUNT($G62:$DE62)</f>
         <v>0</v>
       </c>
       <c r="F57" s="24"/>
@@ -23766,7 +22986,7 @@
         <v/>
       </c>
       <c r="CI57" s="1" t="str">
-        <f t="shared" ref="BT57:CI58" si="114">IF(AND(CI$5&gt;=$C57,CI$5&lt;=$D57),1,"")</f>
+        <f t="shared" si="107"/>
         <v/>
       </c>
       <c r="CJ57" s="1" t="str">
@@ -23830,7 +23050,7 @@
         <v/>
       </c>
       <c r="CY57" s="1" t="str">
-        <f t="shared" ref="CJ57:CY58" si="115">IF(AND(CY$5&gt;=$C57,CY$5&lt;=$D57),1,"")</f>
+        <f t="shared" si="108"/>
         <v/>
       </c>
       <c r="CZ57" s="1" t="str">
@@ -23864,434 +23084,1280 @@
       <c r="C58" s="31"/>
       <c r="D58" s="31"/>
       <c r="E58" s="9">
+        <f>COUNT($G58:$DE58)</f>
+        <v>0</v>
+      </c>
+      <c r="F58" s="24"/>
+      <c r="G58" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="H58" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="I58" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="J58" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="K58" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="L58" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="M58" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="N58" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="O58" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="P58" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="Q58" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="R58" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="S58" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="T58" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="U58" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="V58" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="W58" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="X58" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="Y58" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="Z58" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AA58" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AB58" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AC58" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AD58" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AE58" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AF58" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AG58" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AH58" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AI58" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AJ58" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AK58" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AL58" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AM58" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AN58" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AO58" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AP58" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AQ58" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AR58" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AS58" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AT58" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AU58" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AV58" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AW58" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AX58" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AY58" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AZ58" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="BA58" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="BB58" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="BC58" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BD58" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BE58" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BF58" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BG58" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BH58" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BI58" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BJ58" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BK58" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BL58" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BM58" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BN58" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BO58" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BP58" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BQ58" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BR58" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BS58" s="1" t="str">
+        <f t="shared" si="110"/>
+        <v/>
+      </c>
+      <c r="BT58" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="BU58" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="BV58" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="BW58" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="BX58" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="BY58" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="BZ58" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="CA58" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="CB58" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="CC58" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="CD58" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="CE58" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="CF58" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="CG58" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="CH58" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="CI58" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="CJ58" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CK58" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CL58" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CM58" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CN58" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CO58" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CP58" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CQ58" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CR58" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CS58" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CT58" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CU58" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CV58" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CW58" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CX58" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CY58" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CZ58" s="1" t="str">
+        <f t="shared" si="106"/>
+        <v/>
+      </c>
+      <c r="DA58" s="1" t="str">
+        <f t="shared" si="106"/>
+        <v/>
+      </c>
+      <c r="DB58" s="1" t="str">
+        <f t="shared" si="106"/>
+        <v/>
+      </c>
+      <c r="DC58" s="1" t="str">
+        <f t="shared" si="106"/>
+        <v/>
+      </c>
+      <c r="DD58" s="1" t="str">
+        <f t="shared" si="106"/>
+        <v/>
+      </c>
+      <c r="DE58" s="1" t="str">
+        <f t="shared" si="106"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:109" x14ac:dyDescent="0.45">
+      <c r="A59" s="11"/>
+      <c r="B59" s="34"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="31"/>
+      <c r="E59" s="9">
+        <f>COUNT($G59:$DE59)</f>
+        <v>0</v>
+      </c>
+      <c r="F59" s="24"/>
+      <c r="G59" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="H59" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="I59" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="J59" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="K59" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="L59" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="M59" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="N59" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="O59" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="P59" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="Q59" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="R59" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="S59" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="T59" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="U59" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="V59" s="1" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="W59" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="X59" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="Y59" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="Z59" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AA59" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AB59" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AC59" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AD59" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AE59" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AF59" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AG59" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AH59" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AI59" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AJ59" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AK59" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AL59" s="1" t="str">
+        <f t="shared" si="111"/>
+        <v/>
+      </c>
+      <c r="AM59" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AN59" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AO59" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AP59" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AQ59" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AR59" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AS59" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AT59" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AU59" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AV59" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AW59" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AX59" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AY59" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="AZ59" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="BA59" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="BB59" s="1" t="str">
+        <f t="shared" si="112"/>
+        <v/>
+      </c>
+      <c r="BC59" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BD59" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BE59" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BF59" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BG59" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BH59" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BI59" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BJ59" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BK59" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BL59" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BM59" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BN59" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BO59" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BP59" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BQ59" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BR59" s="1" t="str">
+        <f t="shared" si="113"/>
+        <v/>
+      </c>
+      <c r="BS59" s="1" t="str">
+        <f t="shared" si="110"/>
+        <v/>
+      </c>
+      <c r="BT59" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="BU59" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="BV59" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="BW59" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="BX59" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="BY59" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="BZ59" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="CA59" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="CB59" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="CC59" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="CD59" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="CE59" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="CF59" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="CG59" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="CH59" s="1" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="CI59" s="1" t="str">
+        <f t="shared" ref="BT59:CI60" si="114">IF(AND(CI$5&gt;=$C59,CI$5&lt;=$D59),1,"")</f>
+        <v/>
+      </c>
+      <c r="CJ59" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CK59" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CL59" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CM59" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CN59" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CO59" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CP59" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CQ59" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CR59" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CS59" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CT59" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CU59" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CV59" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CW59" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CX59" s="1" t="str">
+        <f t="shared" si="108"/>
+        <v/>
+      </c>
+      <c r="CY59" s="1" t="str">
+        <f t="shared" ref="CJ59:CY60" si="115">IF(AND(CY$5&gt;=$C59,CY$5&lt;=$D59),1,"")</f>
+        <v/>
+      </c>
+      <c r="CZ59" s="1" t="str">
+        <f t="shared" si="106"/>
+        <v/>
+      </c>
+      <c r="DA59" s="1" t="str">
+        <f t="shared" si="106"/>
+        <v/>
+      </c>
+      <c r="DB59" s="1" t="str">
+        <f t="shared" si="106"/>
+        <v/>
+      </c>
+      <c r="DC59" s="1" t="str">
+        <f t="shared" si="106"/>
+        <v/>
+      </c>
+      <c r="DD59" s="1" t="str">
+        <f t="shared" si="106"/>
+        <v/>
+      </c>
+      <c r="DE59" s="1" t="str">
+        <f t="shared" si="106"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:109" x14ac:dyDescent="0.45">
+      <c r="A60" s="11"/>
+      <c r="B60" s="34"/>
+      <c r="C60" s="31"/>
+      <c r="D60" s="31"/>
+      <c r="E60" s="9">
         <f>COUNT(#REF!)</f>
         <v>0</v>
       </c>
-      <c r="F58" s="24"/>
-      <c r="G58" s="1" t="str">
-        <f t="shared" ref="G58:V58" si="116">IF(AND(G$5&gt;=$C58,G$5&lt;=$D58),1,"")</f>
-        <v/>
-      </c>
-      <c r="H58" s="1" t="str">
+      <c r="F60" s="24"/>
+      <c r="G60" s="1" t="str">
+        <f t="shared" ref="G60:V60" si="116">IF(AND(G$5&gt;=$C60,G$5&lt;=$D60),1,"")</f>
+        <v/>
+      </c>
+      <c r="H60" s="1" t="str">
         <f t="shared" si="116"/>
         <v/>
       </c>
-      <c r="I58" s="1" t="str">
+      <c r="I60" s="1" t="str">
         <f t="shared" si="116"/>
         <v/>
       </c>
-      <c r="J58" s="1" t="str">
+      <c r="J60" s="1" t="str">
         <f t="shared" si="116"/>
         <v/>
       </c>
-      <c r="K58" s="1" t="str">
+      <c r="K60" s="1" t="str">
         <f t="shared" si="116"/>
         <v/>
       </c>
-      <c r="L58" s="1" t="str">
+      <c r="L60" s="1" t="str">
         <f t="shared" si="116"/>
         <v/>
       </c>
-      <c r="M58" s="1" t="str">
+      <c r="M60" s="1" t="str">
         <f t="shared" si="116"/>
         <v/>
       </c>
-      <c r="N58" s="1" t="str">
+      <c r="N60" s="1" t="str">
         <f t="shared" si="116"/>
         <v/>
       </c>
-      <c r="O58" s="1" t="str">
+      <c r="O60" s="1" t="str">
         <f t="shared" si="116"/>
         <v/>
       </c>
-      <c r="P58" s="1" t="str">
+      <c r="P60" s="1" t="str">
         <f t="shared" si="116"/>
         <v/>
       </c>
-      <c r="Q58" s="1" t="str">
+      <c r="Q60" s="1" t="str">
         <f t="shared" si="116"/>
         <v/>
       </c>
-      <c r="R58" s="1" t="str">
+      <c r="R60" s="1" t="str">
         <f t="shared" si="116"/>
         <v/>
       </c>
-      <c r="S58" s="1" t="str">
+      <c r="S60" s="1" t="str">
         <f t="shared" si="116"/>
         <v/>
       </c>
-      <c r="T58" s="1" t="str">
+      <c r="T60" s="1" t="str">
         <f t="shared" si="116"/>
         <v/>
       </c>
-      <c r="U58" s="1" t="str">
+      <c r="U60" s="1" t="str">
         <f t="shared" si="116"/>
         <v/>
       </c>
-      <c r="V58" s="1" t="str">
+      <c r="V60" s="1" t="str">
         <f t="shared" si="116"/>
         <v/>
       </c>
-      <c r="W58" s="1" t="str">
+      <c r="W60" s="1" t="str">
         <f t="shared" si="111"/>
         <v/>
       </c>
-      <c r="X58" s="1" t="str">
+      <c r="X60" s="1" t="str">
         <f t="shared" si="111"/>
         <v/>
       </c>
-      <c r="Y58" s="1" t="str">
+      <c r="Y60" s="1" t="str">
         <f t="shared" si="111"/>
         <v/>
       </c>
-      <c r="Z58" s="1" t="str">
+      <c r="Z60" s="1" t="str">
         <f t="shared" si="111"/>
         <v/>
       </c>
-      <c r="AA58" s="1" t="str">
+      <c r="AA60" s="1" t="str">
         <f t="shared" si="111"/>
         <v/>
       </c>
-      <c r="AB58" s="1" t="str">
+      <c r="AB60" s="1" t="str">
         <f t="shared" si="111"/>
         <v/>
       </c>
-      <c r="AC58" s="1" t="str">
+      <c r="AC60" s="1" t="str">
         <f t="shared" si="111"/>
         <v/>
       </c>
-      <c r="AD58" s="1" t="str">
+      <c r="AD60" s="1" t="str">
         <f t="shared" si="111"/>
         <v/>
       </c>
-      <c r="AE58" s="1" t="str">
+      <c r="AE60" s="1" t="str">
         <f t="shared" si="111"/>
         <v/>
       </c>
-      <c r="AF58" s="1" t="str">
+      <c r="AF60" s="1" t="str">
         <f t="shared" si="111"/>
         <v/>
       </c>
-      <c r="AG58" s="1" t="str">
+      <c r="AG60" s="1" t="str">
         <f t="shared" si="111"/>
         <v/>
       </c>
-      <c r="AH58" s="1" t="str">
+      <c r="AH60" s="1" t="str">
         <f t="shared" si="111"/>
         <v/>
       </c>
-      <c r="AI58" s="1" t="str">
+      <c r="AI60" s="1" t="str">
         <f t="shared" si="111"/>
         <v/>
       </c>
-      <c r="AJ58" s="1" t="str">
+      <c r="AJ60" s="1" t="str">
         <f t="shared" si="111"/>
         <v/>
       </c>
-      <c r="AK58" s="1" t="str">
+      <c r="AK60" s="1" t="str">
         <f t="shared" si="111"/>
         <v/>
       </c>
-      <c r="AL58" s="1" t="str">
+      <c r="AL60" s="1" t="str">
         <f t="shared" si="111"/>
         <v/>
       </c>
-      <c r="AM58" s="1" t="str">
+      <c r="AM60" s="1" t="str">
         <f t="shared" si="112"/>
         <v/>
       </c>
-      <c r="AN58" s="1" t="str">
+      <c r="AN60" s="1" t="str">
         <f t="shared" si="112"/>
         <v/>
       </c>
-      <c r="AO58" s="1" t="str">
+      <c r="AO60" s="1" t="str">
         <f t="shared" si="112"/>
         <v/>
       </c>
-      <c r="AP58" s="1" t="str">
+      <c r="AP60" s="1" t="str">
         <f t="shared" si="112"/>
         <v/>
       </c>
-      <c r="AQ58" s="1" t="str">
+      <c r="AQ60" s="1" t="str">
         <f t="shared" si="112"/>
         <v/>
       </c>
-      <c r="AR58" s="1" t="str">
+      <c r="AR60" s="1" t="str">
         <f t="shared" si="112"/>
         <v/>
       </c>
-      <c r="AS58" s="1" t="str">
+      <c r="AS60" s="1" t="str">
         <f t="shared" si="112"/>
         <v/>
       </c>
-      <c r="AT58" s="1" t="str">
+      <c r="AT60" s="1" t="str">
         <f t="shared" si="112"/>
         <v/>
       </c>
-      <c r="AU58" s="1" t="str">
+      <c r="AU60" s="1" t="str">
         <f t="shared" si="112"/>
         <v/>
       </c>
-      <c r="AV58" s="1" t="str">
+      <c r="AV60" s="1" t="str">
         <f t="shared" si="112"/>
         <v/>
       </c>
-      <c r="AW58" s="1" t="str">
+      <c r="AW60" s="1" t="str">
         <f t="shared" si="112"/>
         <v/>
       </c>
-      <c r="AX58" s="1" t="str">
+      <c r="AX60" s="1" t="str">
         <f t="shared" si="112"/>
         <v/>
       </c>
-      <c r="AY58" s="1" t="str">
+      <c r="AY60" s="1" t="str">
         <f t="shared" si="112"/>
         <v/>
       </c>
-      <c r="AZ58" s="1" t="str">
+      <c r="AZ60" s="1" t="str">
         <f t="shared" si="112"/>
         <v/>
       </c>
-      <c r="BA58" s="1" t="str">
+      <c r="BA60" s="1" t="str">
         <f t="shared" si="112"/>
         <v/>
       </c>
-      <c r="BB58" s="1" t="str">
+      <c r="BB60" s="1" t="str">
         <f t="shared" si="112"/>
         <v/>
       </c>
-      <c r="BC58" s="1" t="str">
+      <c r="BC60" s="1" t="str">
         <f t="shared" si="113"/>
         <v/>
       </c>
-      <c r="BD58" s="1" t="str">
+      <c r="BD60" s="1" t="str">
         <f t="shared" si="113"/>
         <v/>
       </c>
-      <c r="BE58" s="1" t="str">
+      <c r="BE60" s="1" t="str">
         <f t="shared" si="113"/>
         <v/>
       </c>
-      <c r="BF58" s="1" t="str">
+      <c r="BF60" s="1" t="str">
         <f t="shared" si="113"/>
         <v/>
       </c>
-      <c r="BG58" s="1" t="str">
+      <c r="BG60" s="1" t="str">
         <f t="shared" si="113"/>
         <v/>
       </c>
-      <c r="BH58" s="1" t="str">
+      <c r="BH60" s="1" t="str">
         <f t="shared" si="113"/>
         <v/>
       </c>
-      <c r="BI58" s="1" t="str">
+      <c r="BI60" s="1" t="str">
         <f t="shared" si="113"/>
         <v/>
       </c>
-      <c r="BJ58" s="1" t="str">
+      <c r="BJ60" s="1" t="str">
         <f t="shared" si="113"/>
         <v/>
       </c>
-      <c r="BK58" s="1" t="str">
+      <c r="BK60" s="1" t="str">
         <f t="shared" si="113"/>
         <v/>
       </c>
-      <c r="BL58" s="1" t="str">
+      <c r="BL60" s="1" t="str">
         <f t="shared" si="113"/>
         <v/>
       </c>
-      <c r="BM58" s="1" t="str">
+      <c r="BM60" s="1" t="str">
         <f t="shared" si="113"/>
         <v/>
       </c>
-      <c r="BN58" s="1" t="str">
+      <c r="BN60" s="1" t="str">
         <f t="shared" si="113"/>
         <v/>
       </c>
-      <c r="BO58" s="1" t="str">
+      <c r="BO60" s="1" t="str">
         <f t="shared" si="113"/>
         <v/>
       </c>
-      <c r="BP58" s="1" t="str">
+      <c r="BP60" s="1" t="str">
         <f t="shared" si="113"/>
         <v/>
       </c>
-      <c r="BQ58" s="1" t="str">
+      <c r="BQ60" s="1" t="str">
         <f t="shared" si="113"/>
         <v/>
       </c>
-      <c r="BR58" s="1" t="str">
+      <c r="BR60" s="1" t="str">
         <f t="shared" si="113"/>
         <v/>
       </c>
-      <c r="BS58" s="1" t="str">
+      <c r="BS60" s="1" t="str">
         <f t="shared" si="110"/>
         <v/>
       </c>
-      <c r="BT58" s="1" t="str">
+      <c r="BT60" s="1" t="str">
         <f t="shared" si="114"/>
         <v/>
       </c>
-      <c r="BU58" s="1" t="str">
+      <c r="BU60" s="1" t="str">
         <f t="shared" si="114"/>
         <v/>
       </c>
-      <c r="BV58" s="1" t="str">
+      <c r="BV60" s="1" t="str">
         <f t="shared" si="114"/>
         <v/>
       </c>
-      <c r="BW58" s="1" t="str">
+      <c r="BW60" s="1" t="str">
         <f t="shared" si="114"/>
         <v/>
       </c>
-      <c r="BX58" s="1" t="str">
+      <c r="BX60" s="1" t="str">
         <f t="shared" si="114"/>
         <v/>
       </c>
-      <c r="BY58" s="1" t="str">
+      <c r="BY60" s="1" t="str">
         <f t="shared" si="114"/>
         <v/>
       </c>
-      <c r="BZ58" s="1" t="str">
+      <c r="BZ60" s="1" t="str">
         <f t="shared" si="114"/>
         <v/>
       </c>
-      <c r="CA58" s="1" t="str">
+      <c r="CA60" s="1" t="str">
         <f t="shared" si="114"/>
         <v/>
       </c>
-      <c r="CB58" s="1" t="str">
+      <c r="CB60" s="1" t="str">
         <f t="shared" si="114"/>
         <v/>
       </c>
-      <c r="CC58" s="1" t="str">
+      <c r="CC60" s="1" t="str">
         <f t="shared" si="114"/>
         <v/>
       </c>
-      <c r="CD58" s="1" t="str">
+      <c r="CD60" s="1" t="str">
         <f t="shared" si="114"/>
         <v/>
       </c>
-      <c r="CE58" s="1" t="str">
+      <c r="CE60" s="1" t="str">
         <f t="shared" si="114"/>
         <v/>
       </c>
-      <c r="CF58" s="1" t="str">
+      <c r="CF60" s="1" t="str">
         <f t="shared" si="114"/>
         <v/>
       </c>
-      <c r="CG58" s="1" t="str">
+      <c r="CG60" s="1" t="str">
         <f t="shared" si="114"/>
         <v/>
       </c>
-      <c r="CH58" s="1" t="str">
+      <c r="CH60" s="1" t="str">
         <f t="shared" si="114"/>
         <v/>
       </c>
-      <c r="CI58" s="1" t="str">
+      <c r="CI60" s="1" t="str">
         <f t="shared" si="114"/>
         <v/>
       </c>
-      <c r="CJ58" s="1" t="str">
+      <c r="CJ60" s="1" t="str">
         <f t="shared" si="115"/>
         <v/>
       </c>
-      <c r="CK58" s="1" t="str">
+      <c r="CK60" s="1" t="str">
         <f t="shared" si="115"/>
         <v/>
       </c>
-      <c r="CL58" s="1" t="str">
+      <c r="CL60" s="1" t="str">
         <f t="shared" si="115"/>
         <v/>
       </c>
-      <c r="CM58" s="1" t="str">
+      <c r="CM60" s="1" t="str">
         <f t="shared" si="115"/>
         <v/>
       </c>
-      <c r="CN58" s="1" t="str">
+      <c r="CN60" s="1" t="str">
         <f t="shared" si="115"/>
         <v/>
       </c>
-      <c r="CO58" s="1" t="str">
+      <c r="CO60" s="1" t="str">
         <f t="shared" si="115"/>
         <v/>
       </c>
-      <c r="CP58" s="1" t="str">
+      <c r="CP60" s="1" t="str">
         <f t="shared" si="115"/>
         <v/>
       </c>
-      <c r="CQ58" s="1" t="str">
+      <c r="CQ60" s="1" t="str">
         <f t="shared" si="115"/>
         <v/>
       </c>
-      <c r="CR58" s="1" t="str">
+      <c r="CR60" s="1" t="str">
         <f t="shared" si="115"/>
         <v/>
       </c>
-      <c r="CS58" s="1" t="str">
+      <c r="CS60" s="1" t="str">
         <f t="shared" si="115"/>
         <v/>
       </c>
-      <c r="CT58" s="1" t="str">
+      <c r="CT60" s="1" t="str">
         <f t="shared" si="115"/>
         <v/>
       </c>
-      <c r="CU58" s="1" t="str">
+      <c r="CU60" s="1" t="str">
         <f t="shared" si="115"/>
         <v/>
       </c>
-      <c r="CV58" s="1" t="str">
+      <c r="CV60" s="1" t="str">
         <f t="shared" si="115"/>
         <v/>
       </c>
-      <c r="CW58" s="1" t="str">
+      <c r="CW60" s="1" t="str">
         <f t="shared" si="115"/>
         <v/>
       </c>
-      <c r="CX58" s="1" t="str">
+      <c r="CX60" s="1" t="str">
         <f t="shared" si="115"/>
         <v/>
       </c>
-      <c r="CY58" s="1" t="str">
+      <c r="CY60" s="1" t="str">
         <f t="shared" si="115"/>
         <v/>
       </c>
-      <c r="CZ58" s="1" t="str">
-        <f t="shared" ref="CZ58:DE58" si="117">IF(AND(CZ$5&gt;=$C58,CZ$5&lt;=$D58),1,"")</f>
-        <v/>
-      </c>
-      <c r="DA58" s="1" t="str">
+      <c r="CZ60" s="1" t="str">
+        <f t="shared" ref="CZ60:DE60" si="117">IF(AND(CZ$5&gt;=$C60,CZ$5&lt;=$D60),1,"")</f>
+        <v/>
+      </c>
+      <c r="DA60" s="1" t="str">
         <f t="shared" si="117"/>
         <v/>
       </c>
-      <c r="DB58" s="1" t="str">
+      <c r="DB60" s="1" t="str">
         <f t="shared" si="117"/>
         <v/>
       </c>
-      <c r="DC58" s="1" t="str">
+      <c r="DC60" s="1" t="str">
         <f t="shared" si="117"/>
         <v/>
       </c>
-      <c r="DD58" s="1" t="str">
+      <c r="DD60" s="1" t="str">
         <f t="shared" si="117"/>
         <v/>
       </c>
-      <c r="DE58" s="1" t="str">
+      <c r="DE60" s="1" t="str">
         <f t="shared" si="117"/>
         <v/>
       </c>
     </row>
   </sheetData>
   <sheetProtection insertRows="0"/>
-  <autoFilter ref="A6:F32"/>
+  <autoFilter ref="A6:F33"/>
   <phoneticPr fontId="19"/>
-  <conditionalFormatting sqref="G7:DE58">
+  <conditionalFormatting sqref="G7:DE60">
     <cfRule type="cellIs" dxfId="0" priority="12" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F20:F26 F37:F41 F28:F32 F9:F18 F34:F35 F49:F51 F43:F47 F54:F58">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F21:F27 F39:F43 F29:F33 F9:F19 F35:F37 F51:F53 F45:F49 F56:F60">
       <formula1>"作業中,保留,削除,完了"</formula1>
     </dataValidation>
   </dataValidations>

--- a/概要/ガントチャート_舞台劇.xlsx
+++ b/概要/ガントチャート_舞台劇.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="51">
   <si>
     <t>ガントチャート</t>
     <phoneticPr fontId="19"/>
@@ -360,6 +360,19 @@
       <t>コウゲキ</t>
     </rPh>
     <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>攻撃ヒット時のカメラシェイク</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>作業中</t>
   </si>
 </sst>
 </file>
@@ -4744,10 +4757,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="31">
-        <v>45954</v>
+        <v>45951</v>
       </c>
       <c r="D13" s="31">
-        <v>45955</v>
+        <v>45952</v>
       </c>
       <c r="E13" s="9">
         <f t="shared" si="81"/>
@@ -5012,25 +5025,25 @@
         <f t="shared" si="84"/>
         <v/>
       </c>
-      <c r="BS13" s="1" t="str">
+      <c r="BS13" s="1">
         <f t="shared" ref="H13:BS17" si="85">IF(AND(BS$5&gt;=$C13,BS$5&lt;=$D13),1,"")</f>
-        <v/>
-      </c>
-      <c r="BT13" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="BT13" s="1">
         <f t="shared" si="78"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BU13" s="1" t="str">
         <f t="shared" si="78"/>
         <v/>
       </c>
-      <c r="BV13" s="1">
+      <c r="BV13" s="1" t="str">
         <f t="shared" si="78"/>
-        <v>1</v>
-      </c>
-      <c r="BW13" s="1">
+        <v/>
+      </c>
+      <c r="BW13" s="1" t="str">
         <f t="shared" si="78"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="BX13" s="1" t="str">
         <f t="shared" si="78"/>
@@ -5177,14 +5190,14 @@
         <v>1</v>
       </c>
       <c r="C14" s="31">
-        <v>45954</v>
+        <v>45951</v>
       </c>
       <c r="D14" s="31">
-        <v>45955</v>
+        <v>45951</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="81"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="24" t="s">
         <v>26</v>
@@ -5445,9 +5458,9 @@
         <f t="shared" si="85"/>
         <v/>
       </c>
-      <c r="BS14" s="1" t="str">
-        <f t="shared" si="85"/>
-        <v/>
+      <c r="BS14" s="1">
+        <f t="shared" si="85"/>
+        <v>1</v>
       </c>
       <c r="BT14" s="1" t="str">
         <f t="shared" ref="BT14:CI30" si="87">IF(AND(BT$5&gt;=$C14,BT$5&lt;=$D14),1,"")</f>
@@ -5457,13 +5470,13 @@
         <f t="shared" si="87"/>
         <v/>
       </c>
-      <c r="BV14" s="1">
-        <f t="shared" si="87"/>
-        <v>1</v>
-      </c>
-      <c r="BW14" s="1">
-        <f t="shared" si="87"/>
-        <v>1</v>
+      <c r="BV14" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BW14" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
       </c>
       <c r="BX14" s="1" t="str">
         <f t="shared" si="87"/>
@@ -5610,14 +5623,14 @@
         <v>1</v>
       </c>
       <c r="C15" s="31">
-        <v>45956</v>
+        <v>45952</v>
       </c>
       <c r="D15" s="31">
-        <v>45959</v>
+        <v>45952</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="81"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F15" s="24" t="s">
         <v>26</v>
@@ -5882,9 +5895,9 @@
         <f t="shared" si="85"/>
         <v/>
       </c>
-      <c r="BT15" s="1" t="str">
-        <f t="shared" si="87"/>
-        <v/>
+      <c r="BT15" s="1">
+        <f t="shared" si="87"/>
+        <v>1</v>
       </c>
       <c r="BU15" s="1" t="str">
         <f t="shared" si="87"/>
@@ -5898,21 +5911,21 @@
         <f t="shared" si="87"/>
         <v/>
       </c>
-      <c r="BX15" s="1">
-        <f t="shared" si="87"/>
-        <v>1</v>
-      </c>
-      <c r="BY15" s="1">
-        <f t="shared" si="87"/>
-        <v>1</v>
-      </c>
-      <c r="BZ15" s="1">
-        <f t="shared" si="87"/>
-        <v>1</v>
-      </c>
-      <c r="CA15" s="1">
-        <f t="shared" si="87"/>
-        <v>1</v>
+      <c r="BX15" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BY15" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BZ15" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="CA15" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
       </c>
       <c r="CB15" s="1" t="str">
         <f t="shared" si="87"/>
@@ -6040,15 +6053,11 @@
         <v>48</v>
       </c>
       <c r="B16" s="34"/>
-      <c r="C16" s="31">
-        <v>45960</v>
-      </c>
-      <c r="D16" s="31">
-        <v>45962</v>
-      </c>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
       <c r="E16" s="9">
         <f t="shared" si="81"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F16" s="24"/>
       <c r="G16" s="1" t="str">
@@ -6343,17 +6352,17 @@
         <f t="shared" si="87"/>
         <v/>
       </c>
-      <c r="CB16" s="1">
-        <f t="shared" si="87"/>
-        <v>1</v>
-      </c>
-      <c r="CC16" s="1">
-        <f t="shared" si="87"/>
-        <v>1</v>
-      </c>
-      <c r="CD16" s="1">
-        <f t="shared" si="87"/>
-        <v>1</v>
+      <c r="CB16" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="CC16" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="CD16" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
       </c>
       <c r="CE16" s="1" t="str">
         <f t="shared" si="87"/>
@@ -6469,15 +6478,11 @@
         <v>42</v>
       </c>
       <c r="B17" s="34"/>
-      <c r="C17" s="31">
-        <v>45960</v>
-      </c>
-      <c r="D17" s="31">
-        <v>45962</v>
-      </c>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
       <c r="E17" s="9">
         <f t="shared" si="81"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F17" s="24"/>
       <c r="G17" s="1" t="str">
@@ -6772,17 +6777,17 @@
         <f t="shared" si="87"/>
         <v/>
       </c>
-      <c r="CB17" s="1">
-        <f t="shared" si="87"/>
-        <v>1</v>
-      </c>
-      <c r="CC17" s="1">
-        <f t="shared" si="87"/>
-        <v>1</v>
-      </c>
-      <c r="CD17" s="1">
-        <f t="shared" si="87"/>
-        <v>1</v>
+      <c r="CB17" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="CC17" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="CD17" s="1" t="str">
+        <f t="shared" si="87"/>
+        <v/>
       </c>
       <c r="CE17" s="1" t="str">
         <f t="shared" si="87"/>
@@ -6894,12 +6899,20 @@
       </c>
     </row>
     <row r="18" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="43"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="31"/>
+      <c r="A18" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="34">
+        <v>0.5</v>
+      </c>
+      <c r="C18" s="31">
+        <v>45952</v>
+      </c>
       <c r="D18" s="31"/>
       <c r="E18" s="9"/>
-      <c r="F18" s="24"/>
+      <c r="F18" s="24" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="19" spans="1:109" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="36"/>
@@ -14995,14 +15008,14 @@
         <v>1</v>
       </c>
       <c r="C39" s="31">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="D39" s="31">
-        <v>45952</v>
+        <v>45951</v>
       </c>
       <c r="E39" s="9">
         <f>COUNT($G39:$DE39)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F39" s="24" t="s">
         <v>26</v>
@@ -15247,17 +15260,17 @@
         <f t="shared" si="99"/>
         <v/>
       </c>
-      <c r="BO39" s="1">
+      <c r="BO39" s="1" t="str">
         <f t="shared" si="99"/>
-        <v>1</v>
-      </c>
-      <c r="BP39" s="1">
+        <v/>
+      </c>
+      <c r="BP39" s="1" t="str">
         <f t="shared" si="99"/>
-        <v>1</v>
-      </c>
-      <c r="BQ39" s="1">
+        <v/>
+      </c>
+      <c r="BQ39" s="1" t="str">
         <f t="shared" si="99"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="BR39" s="1">
         <f t="shared" si="92"/>
@@ -15267,9 +15280,9 @@
         <f t="shared" si="89"/>
         <v>1</v>
       </c>
-      <c r="BT39" s="1">
+      <c r="BT39" s="1" t="str">
         <f t="shared" si="89"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="BU39" s="1" t="str">
         <f t="shared" si="89"/>
@@ -24622,6 +24635,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847">
@@ -24637,15 +24659,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24668,6 +24681,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -24676,12 +24697,4 @@
     <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>